--- a/generated/spreadsheet/technical-details-consent-technical-details-consent.xlsx
+++ b/generated/spreadsheet/technical-details-consent-technical-details-consent.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I151"/>
+  <dimension ref="A1:I150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -568,14 +568,14 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Application sub type</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Further classification of the application type for specific variations within the main application type</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -599,19 +599,19 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Submission date</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>Date the application is submitted in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -630,19 +630,19 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Modules[]</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>List of required modules for this application that can be used to validate the application</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -661,14 +661,18 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
+          <t>Documents[]</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -697,13 +701,13 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -732,13 +736,13 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -748,7 +752,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -767,23 +771,23 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -802,18 +806,18 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Uploaded date</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -837,23 +841,27 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Base64</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -877,12 +885,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Base64</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -892,7 +900,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -916,12 +924,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -931,7 +939,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -955,17 +963,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>File size</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -984,22 +992,18 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
+          <t>Fee</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>File size</t>
-        </is>
-      </c>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1009,7 +1013,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1028,13 +1032,13 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1063,75 +1067,67 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Transactions[]</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Access and rights of way</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Fee</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Transactions[]</t>
-        </is>
-      </c>
+          <t>New or altered vehicle access</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Access and rights of way</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>New or altered vehicle access</t>
+          <t>New or altered pedestrian access</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
@@ -1139,7 +1135,7 @@
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
+          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1158,20 +1154,24 @@
       <c r="B21" s="2" t="n"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>New or altered pedestrian access</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1181,23 +1181,27 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n"/>
-      <c r="B22" s="2" t="n"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1212,27 +1216,23 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1256,14 +1256,18 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1273,7 +1277,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1292,18 +1296,18 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1313,51 +1317,47 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n"/>
-      <c r="B26" s="2" t="n"/>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="n"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>agent</t>
@@ -1365,14 +1365,18 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1382,7 +1386,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1401,13 +1405,13 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1417,7 +1421,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1436,13 +1440,13 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1471,13 +1475,13 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1506,13 +1510,13 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1522,7 +1526,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1536,18 +1540,14 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1571,19 +1571,19 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>User role</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -1593,58 +1593,58 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n"/>
-      <c r="B34" s="2" t="n"/>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>User role</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1668,14 +1668,18 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1685,7 +1689,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1704,18 +1708,18 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -1725,51 +1729,47 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n"/>
-      <c r="B38" s="2" t="n"/>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Applicants[]</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="2" t="n"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1777,14 +1777,18 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1794,7 +1798,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1813,13 +1817,13 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1829,7 +1833,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1848,13 +1852,13 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -1883,13 +1887,13 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -1918,13 +1922,13 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -1934,59 +1938,51 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="n"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity, geological and archaeological conservation</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
+        </is>
+      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Protected species impact</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Where is there a likelihood of protected and priority species being affected?</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity, geological and archaeological conservation</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Protected species impact</t>
+          <t>Biodiversity features impact</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -1994,7 +1990,7 @@
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of protected and priority species being affected?</t>
+          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2013,7 +2009,7 @@
       <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity features impact</t>
+          <t>Geological features impact</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
@@ -2021,7 +2017,7 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
+          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2036,119 +2032,119 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n"/>
-      <c r="B47" s="2" t="n"/>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Geological features impact</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity net gain</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr"/>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>National requirement types[]</t>
+        </is>
+      </c>
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>List of the document types required for the given application type</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Conflict of interest</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr"/>
       <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>List of the document types required for the given application type</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Conflict of interest</t>
+          <t>Declaration</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr"/>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
       <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>A name of a person</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -2156,12 +2152,12 @@
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2175,7 +2171,7 @@
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
@@ -2183,12 +2179,12 @@
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2198,24 +2194,36 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n"/>
-      <c r="B53" s="2" t="n"/>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>How the proposed development will impact existing and proposed employee numbers</t>
+        </is>
+      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr"/>
+          <t>Existing employees</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2225,16 +2233,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>How the proposed development will impact existing and proposed employee numbers</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="n"/>
+      <c r="B54" s="2" t="n"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Existing employees</t>
@@ -2242,14 +2242,14 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2273,14 +2273,14 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2299,19 +2299,19 @@
       <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
+          <t>Proposed employees</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2335,14 +2335,14 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2366,14 +2366,14 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2388,28 +2388,36 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n"/>
-      <c r="B59" s="2" t="n"/>
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Existing use</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>How the site is currently being used.</t>
+        </is>
+      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Existing use details[]</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -2419,16 +2427,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Existing use</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>How the site is currently being used.</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Existing use details[]</t>
@@ -2436,24 +2436,24 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Use details</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Further detail of the use</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2467,14 +2467,14 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Use details</t>
+          <t>Land part</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Further detail of the use</t>
+          <t>Which part of the land the use relates to</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2493,24 +2493,20 @@
       <c r="B62" s="2" t="n"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>Land part</t>
-        </is>
-      </c>
+          <t>Site vacant</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr"/>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Which part of the land the use relates to</t>
+          <t>Is the site currently vacant</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -2524,7 +2520,7 @@
       <c r="B63" s="2" t="n"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Site vacant</t>
+          <t>Last use details</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr"/>
@@ -2532,17 +2528,17 @@
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Is the site currently vacant</t>
+          <t>Description of the last use of the site</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2547,7 @@
       <c r="B64" s="2" t="n"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Last use details</t>
+          <t>Last use end date</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
@@ -2559,12 +2555,12 @@
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Description of the last use of the site</t>
+          <t>Date the last use ended (YYYY-MM-DD format)</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -2578,7 +2574,7 @@
       <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Last use end date</t>
+          <t>Is contaminated land</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
@@ -2586,17 +2582,17 @@
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Date the last use ended (YYYY-MM-DD format)</t>
+          <t>Is the site known to be contaminated?</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2601,7 @@
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Is contaminated land</t>
+          <t>Is suspected contaminated land</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
@@ -2613,7 +2609,7 @@
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Is the site known to be contaminated?</t>
+          <t>Is the site suspected of contamination?</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -2632,7 +2628,7 @@
       <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Is suspected contaminated land</t>
+          <t>Proposed use contamination risk</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
@@ -2640,7 +2636,7 @@
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Is the site suspected of contamination?</t>
+          <t>Is the proposed use vulnerable to the presence of contamination?</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -2659,7 +2655,7 @@
       <c r="B68" s="2" t="n"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Proposed use contamination risk</t>
+          <t>Contamination assessment</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
@@ -2667,26 +2663,34 @@
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Is the proposed use vulnerable to the presence of contamination?</t>
+          <t>Reference to contamination assessment document</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n"/>
-      <c r="B69" s="2" t="n"/>
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Flood risk assessment</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Results of any flood risk assessments made for the development site</t>
+        </is>
+      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Contamination assessment</t>
+          <t>Flood risk area</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
@@ -2694,34 +2698,26 @@
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Reference to contamination assessment document</t>
+          <t>Is the site within an area at risk of flooding?</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Flood risk assessment</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Results of any flood risk assessments made for the development site</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="n"/>
+      <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Flood risk area</t>
+          <t>Data provided by</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
@@ -2729,17 +2725,17 @@
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Is the site within an area at risk of flooding?</t>
+          <t>Who provided the data: Applicant or System/Service?</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2744,7 @@
       <c r="B71" s="2" t="n"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Data provided by</t>
+          <t>Flood risk assessment</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
@@ -2756,12 +2752,12 @@
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Who provided the data: Applicant or System/Service?</t>
+          <t>Reference of the flood risk assessment document</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -2775,7 +2771,7 @@
       <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Flood risk assessment</t>
+          <t>Within 20m watercourse</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
@@ -2783,17 +2779,17 @@
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Reference of the flood risk assessment document</t>
+          <t>Whether the development is within 20 metres of a watercourse</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2798,7 @@
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Within 20m watercourse</t>
+          <t>Increases flood risk</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
@@ -2810,7 +2806,7 @@
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Whether the development is within 20 metres of a watercourse</t>
+          <t>Whether the development increases flood risk</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -2829,7 +2825,7 @@
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Increases flood risk</t>
+          <t>Surface water disposal[]</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
@@ -2837,12 +2833,12 @@
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Whether the development increases flood risk</t>
+          <t>Method for disposing of surface water</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -2852,11 +2848,19 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n"/>
-      <c r="B75" s="2" t="n"/>
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Foul sewage disposal</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>How waste water will leave the property as part of the proposed development</t>
+        </is>
+      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Surface water disposal[]</t>
+          <t>Has new disposal arrangements</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
@@ -2864,12 +2868,12 @@
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Method for disposing of surface water</t>
+          <t>Does the proposal include any new foul sewage disposal arrangments</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -2879,19 +2883,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Foul sewage disposal</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>How waste water will leave the property as part of the proposed development</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="n"/>
+      <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Has new disposal arrangements</t>
+          <t>Foul sewage disposal types[]</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
@@ -2899,17 +2895,17 @@
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include any new foul sewage disposal arrangments</t>
+          <t>List of ways foul sewage will be disposed of</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2914,7 @@
       <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Foul sewage disposal types[]</t>
+          <t>Connect to drainage system</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
@@ -2926,17 +2922,17 @@
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>List of ways foul sewage will be disposed of</t>
+          <t>Whether the proposal needs to connect to the existing drainage system</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2945,20 +2941,24 @@
       <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Connect to drainage system</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E78" s="2" t="inlineStr"/>
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal needs to connect to the existing drainage system</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -2968,45 +2968,33 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n"/>
-      <c r="B79" s="2" t="n"/>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Hazardous substances</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Details of hazardous substances requiring consent used as part of the development</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr"/>
+      <c r="D79" s="2" t="inlineStr"/>
       <c r="E79" s="2" t="inlineStr"/>
       <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>A unique reference for the data item</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Hazardous substances</t>
+          <t>Hours of operation</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Details of hazardous substances requiring consent used as part of the development</t>
+          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr"/>
@@ -3020,33 +3008,45 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr"/>
-      <c r="D81" s="2" t="inlineStr"/>
+          <t>What materials are being used for the proposed development</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Building elements[]</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Building element type</t>
+        </is>
+      </c>
       <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>What materials are being used for the proposed development</t>
-        </is>
-      </c>
+      <c r="A82" s="2" t="n"/>
+      <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>Building elements[]</t>
@@ -3054,24 +3054,24 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Building element type</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3085,14 +3085,14 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Existing materials</t>
+          <t>Proposed materials</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -3116,19 +3116,19 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Materials not applicable</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>Indicates this building element is not relevant to the application</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -3147,14 +3147,14 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Materials not applicable</t>
+          <t>Materials not known</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Indicates this building element is not relevant to the application</t>
+          <t>Indicates the materials for this building element are not yet known</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -3173,19 +3173,15 @@
       <c r="B86" s="2" t="n"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Materials not known</t>
-        </is>
-      </c>
+          <t>Providing additional material information</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Indicates the materials for this building element are not yet known</t>
+          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -3195,7 +3191,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3204,20 +3200,24 @@
       <c r="B87" s="2" t="n"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Providing additional material information</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -3227,45 +3227,33 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n"/>
-      <c r="B88" s="2" t="n"/>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Non residential floorspace</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Details of changes to non-residential floorspace in the proposed development.</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr"/>
+      <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>A unique reference for the data item</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Non residential floorspace</t>
+          <t>Ownership certificates and agricultural land declaration</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Details of changes to non-residential floorspace in the proposed development.</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr"/>
@@ -3279,36 +3267,44 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificates and agricultural land declaration</t>
+          <t>Pre-application advice</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr"/>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice sought</t>
+        </is>
+      </c>
       <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A91" s="2" t="n"/>
+      <c r="B91" s="2" t="n"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
@@ -3316,17 +3312,17 @@
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3331,7 @@
       <c r="B92" s="2" t="n"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr"/>
@@ -3343,7 +3339,7 @@
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -3362,7 +3358,7 @@
       <c r="B93" s="2" t="n"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
@@ -3370,7 +3366,7 @@
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -3389,7 +3385,7 @@
       <c r="B94" s="2" t="n"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
@@ -3397,7 +3393,7 @@
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -3412,11 +3408,19 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n"/>
-      <c r="B95" s="2" t="n"/>
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Processes machinery waste</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>How waste will be managed on the site</t>
+        </is>
+      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Site activity details</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
@@ -3424,7 +3428,7 @@
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -3434,24 +3438,16 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>Processes machinery waste</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>How waste will be managed on the site</t>
-        </is>
-      </c>
+      <c r="A96" s="2" t="n"/>
+      <c r="B96" s="2" t="n"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Site activity details</t>
+          <t>Proposal waste management</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
@@ -3459,12 +3455,12 @@
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
+          <t>Whether the proposal involves waste management development</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -3478,20 +3474,24 @@
       <c r="B97" s="2" t="n"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Proposal waste management</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr"/>
+          <t>Waste management[]</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Waste management facility type</t>
+        </is>
+      </c>
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves waste management development</t>
+          <t>Type of waste management facility</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -3510,24 +3510,24 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Waste management facility type</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Type of waste management facility</t>
+          <t>Whether the facility is not applicable</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3541,19 +3541,19 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Total capacity</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Whether the facility is not applicable</t>
+          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -3572,19 +3572,19 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Total capacity</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -3603,19 +3603,19 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Annual throughput</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Maximum annual operational throughput in tonnes/litres</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -3634,19 +3634,19 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Annual throughput</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Maximum annual operational throughput in tonnes/litres</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -3660,24 +3660,24 @@
       <c r="B103" s="2" t="n"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
+          <t>Waste streams throughput</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -3696,14 +3696,14 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Construction demolition</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -3727,14 +3727,14 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Construction demolition</t>
+          <t>Commercial industrial</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -3758,14 +3758,14 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Commercial industrial</t>
+          <t>Hazardous</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -3780,82 +3780,82 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n"/>
-      <c r="B107" s="2" t="n"/>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Waste streams throughput</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous</t>
-        </is>
-      </c>
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>What development, works or change of use is proposed</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr"/>
+      <c r="D107" s="2" t="inlineStr"/>
       <c r="E107" s="2" t="inlineStr"/>
       <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Description of the proposal</t>
+          <t>Residential units</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr"/>
+          <t>Details of the residential units that make up both the current and proposed development.</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Residential unit change</t>
+        </is>
+      </c>
       <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr"/>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr"/>
-      <c r="I108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Proposal includes the gain, loss or change of use of residential units</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>Residential units</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>Details of the residential units that make up both the current and proposed development.</t>
-        </is>
-      </c>
+      <c r="A109" s="2" t="n"/>
+      <c r="B109" s="2" t="n"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Residential unit change</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Tenure type</t>
+        </is>
+      </c>
       <c r="E109" s="2" t="inlineStr"/>
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Proposal includes the gain, loss or change of use of residential units</t>
+          <t>Category of housing tenure</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -3874,14 +3874,14 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Tenure type</t>
+          <t>Housing type</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Category of housing tenure</t>
+          <t>Type of housing</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -3905,19 +3905,23 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Housing type</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr"/>
+          <t>Existing unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Units unknown</t>
+        </is>
+      </c>
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Type of housing</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
@@ -3941,13 +3945,17 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -3981,22 +3989,22 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Number of bedrooms</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4020,12 +4028,12 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Number of bedrooms</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -4035,7 +4043,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4054,17 +4062,13 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -4074,7 +4078,7 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4088,28 +4092,28 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Existing unit breakdown[]</t>
+          <t>Proposed unit breakdown[]</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Total units</t>
+          <t>Units unknown</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4128,13 +4132,17 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -4168,22 +4176,22 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Number of bedrooms</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4207,12 +4215,12 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Number of bedrooms</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -4222,7 +4230,7 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4241,17 +4249,13 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -4261,7 +4265,7 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4270,23 +4274,15 @@
       <c r="B121" s="2" t="n"/>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>Proposed unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
-        <is>
-          <t>Total units</t>
-        </is>
-      </c>
+          <t>Total existing units</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr"/>
+      <c r="E121" s="2" t="inlineStr"/>
       <c r="F121" s="2" t="inlineStr"/>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>The total number of existing units</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -4296,7 +4292,7 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4301,7 @@
       <c r="B122" s="2" t="n"/>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Total existing units</t>
+          <t>Total proposed units</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr"/>
@@ -4313,7 +4309,7 @@
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>The total number of existing units</t>
+          <t>The total number of proposed units</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -4332,7 +4328,7 @@
       <c r="B123" s="2" t="n"/>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Total proposed units</t>
+          <t>Net change</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr"/>
@@ -4340,7 +4336,7 @@
       <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>The total number of proposed units</t>
+          <t>Calculated net change in units</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -4355,11 +4351,19 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n"/>
-      <c r="B124" s="2" t="n"/>
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Site area</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>How big the site is including relevant measurements</t>
+        </is>
+      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Net change</t>
+          <t>Site area in hectares</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr"/>
@@ -4367,7 +4371,7 @@
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Calculated net change in units</t>
+          <t>The size of the site in hectares</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -4382,19 +4386,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>Site area</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>How big the site is including relevant measurements</t>
-        </is>
-      </c>
+      <c r="A125" s="2" t="n"/>
+      <c r="B125" s="2" t="n"/>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Site area in hectares</t>
+          <t>Site area provided by</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr"/>
@@ -4402,39 +4398,51 @@
       <c r="F125" s="2" t="inlineStr"/>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>The size of the site in hectares</t>
+          <t>Who provided the site area value</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n"/>
-      <c r="B126" s="2" t="n"/>
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Site area provided by</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Site boundary</t>
+        </is>
+      </c>
       <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Who provided the site area value</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
@@ -4444,16 +4452,8 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A127" s="2" t="n"/>
+      <c r="B127" s="2" t="n"/>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -4461,19 +4461,19 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr"/>
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
@@ -4492,14 +4492,14 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr"/>
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -4523,19 +4523,19 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr"/>
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
@@ -4554,14 +4554,14 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr"/>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -4585,14 +4585,14 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr"/>
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -4616,14 +4616,14 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -4647,19 +4647,19 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr"/>
       <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
@@ -4678,14 +4678,14 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -4700,50 +4700,46 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n"/>
-      <c r="B135" s="2" t="n"/>
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr"/>
       <c r="E135" s="2" t="inlineStr"/>
       <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A136" s="2" t="n"/>
+      <c r="B136" s="2" t="n"/>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr"/>
@@ -4751,12 +4747,12 @@
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
@@ -4770,7 +4766,7 @@
       <c r="B137" s="2" t="n"/>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr"/>
@@ -4778,17 +4774,17 @@
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4797,15 +4793,19 @@
       <c r="B138" s="2" t="n"/>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4829,14 +4829,14 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr"/>
       <c r="F139" s="2" t="inlineStr"/>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -4860,14 +4860,14 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr"/>
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -4882,28 +4882,32 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n"/>
-      <c r="B141" s="2" t="n"/>
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Trade effluent</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
+        </is>
+      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Disposal required</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr"/>
       <c r="E141" s="2" t="inlineStr"/>
       <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
@@ -4913,19 +4917,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>Trade effluent</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
-        </is>
-      </c>
+      <c r="A142" s="2" t="n"/>
+      <c r="B142" s="2" t="n"/>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Disposal required</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr"/>
@@ -4933,77 +4929,81 @@
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
+          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n"/>
-      <c r="B143" s="2" t="n"/>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Trees and hedges information</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr"/>
       <c r="D143" s="2" t="inlineStr"/>
       <c r="E143" s="2" t="inlineStr"/>
       <c r="F143" s="2" t="inlineStr"/>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
-        </is>
-      </c>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I143" s="2" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr"/>
+      <c r="I143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Trees and hedges information</t>
+          <t>Vehicle parking</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr"/>
-      <c r="D144" s="2" t="inlineStr"/>
+          <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Parking spaces[]</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Parking space type</t>
+        </is>
+      </c>
       <c r="E144" s="2" t="inlineStr"/>
       <c r="F144" s="2" t="inlineStr"/>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr"/>
-      <c r="I144" s="2" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>Type of parking space or vehicle type</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>Vehicle parking</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
-        </is>
-      </c>
+      <c r="A145" s="2" t="n"/>
+      <c r="B145" s="2" t="n"/>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>Parking spaces[]</t>
@@ -5011,24 +5011,24 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Parking space type</t>
+          <t>Vehicle type other</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr"/>
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Type of parking space or vehicle type</t>
+          <t>Vehicle type when parking space type is 'other'</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5042,24 +5042,24 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Vehicle type other</t>
+          <t>Total existing</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr"/>
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Vehicle type when parking space type is 'other'</t>
+          <t>Total number of existing parking spaces</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5073,14 +5073,14 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Total existing</t>
+          <t>Total proposed</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr"/>
       <c r="F147" s="2" t="inlineStr"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Total number of existing parking spaces</t>
+          <t>Total number of proposed parking spaces</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -5104,14 +5104,14 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Total proposed</t>
+          <t>Difference in spaces</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr"/>
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Total number of proposed parking spaces</t>
+          <t>Net change in parking spaces (proposed minus existing)</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -5126,50 +5126,46 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n"/>
-      <c r="B149" s="2" t="n"/>
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Waste storage and collection</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
+        </is>
+      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Parking spaces[]</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t>Difference in spaces</t>
-        </is>
-      </c>
+          <t>Waste storage area details</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr"/>
       <c r="E149" s="2" t="inlineStr"/>
       <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Net change in parking spaces (proposed minus existing)</t>
+          <t>Details of the waste storage area including location, size, design and access arrangements</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>Waste storage and collection</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
-        </is>
-      </c>
+      <c r="A150" s="2" t="n"/>
+      <c r="B150" s="2" t="n"/>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Waste storage area details</t>
+          <t>Separate recycling arrangements details</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr"/>
@@ -5177,7 +5173,7 @@
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Details of the waste storage area including location, size, design and access arrangements</t>
+          <t>Details of the recycling arrangements including types of materials, collection methods and storage facilities</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -5186,33 +5182,6 @@
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="n"/>
-      <c r="B151" s="2" t="n"/>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>Separate recycling arrangements details</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr"/>
-      <c r="E151" s="2" t="inlineStr"/>
-      <c r="F151" s="2" t="inlineStr"/>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>Details of the recycling arrangements including types of materials, collection methods and storage facilities</t>
-        </is>
-      </c>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I151" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
@@ -5220,68 +5189,68 @@
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="A144"/>
+    <mergeCell ref="B22:B25"/>
     <mergeCell ref="B49"/>
-    <mergeCell ref="A39:A44"/>
-    <mergeCell ref="B82:B88"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="A81"/>
-    <mergeCell ref="A2:A19"/>
+    <mergeCell ref="B149:B150"/>
+    <mergeCell ref="B75:B78"/>
+    <mergeCell ref="B135:B140"/>
+    <mergeCell ref="B143"/>
+    <mergeCell ref="B26:B33"/>
+    <mergeCell ref="A149:A150"/>
     <mergeCell ref="B89"/>
+    <mergeCell ref="A59:A68"/>
     <mergeCell ref="B80"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B50"/>
-    <mergeCell ref="A96:A107"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="B23:B26"/>
-    <mergeCell ref="A91:A95"/>
+    <mergeCell ref="B59:B68"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="B79"/>
+    <mergeCell ref="B2:B18"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A81:A87"/>
+    <mergeCell ref="A144:A148"/>
+    <mergeCell ref="B95:B106"/>
+    <mergeCell ref="A75:A78"/>
+    <mergeCell ref="A126:A134"/>
     <mergeCell ref="A48"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="B70:B75"/>
-    <mergeCell ref="A109:A124"/>
-    <mergeCell ref="B39:B44"/>
-    <mergeCell ref="B127:B135"/>
-    <mergeCell ref="B136:B141"/>
-    <mergeCell ref="B144"/>
-    <mergeCell ref="A54:A59"/>
-    <mergeCell ref="A60:A69"/>
+    <mergeCell ref="A143"/>
+    <mergeCell ref="B108:B123"/>
+    <mergeCell ref="A69:A74"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="B47"/>
     <mergeCell ref="A49"/>
-    <mergeCell ref="B81"/>
-    <mergeCell ref="B90"/>
-    <mergeCell ref="B27:B34"/>
-    <mergeCell ref="A76:A79"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="B96:B107"/>
-    <mergeCell ref="B54:B59"/>
-    <mergeCell ref="A136:A141"/>
-    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="A107"/>
+    <mergeCell ref="B38:B43"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A79"/>
+    <mergeCell ref="A88"/>
+    <mergeCell ref="A141:A142"/>
+    <mergeCell ref="B144:B148"/>
+    <mergeCell ref="B126:B134"/>
     <mergeCell ref="B48"/>
-    <mergeCell ref="B91:B95"/>
-    <mergeCell ref="B109:B124"/>
-    <mergeCell ref="A127:A135"/>
-    <mergeCell ref="A125:A126"/>
-    <mergeCell ref="B60:B69"/>
-    <mergeCell ref="A90"/>
-    <mergeCell ref="A108"/>
-    <mergeCell ref="A27:A34"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="B69:B74"/>
+    <mergeCell ref="A2:A18"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="B90:B94"/>
+    <mergeCell ref="A135:A140"/>
+    <mergeCell ref="B81:B87"/>
+    <mergeCell ref="B107"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="B53:B58"/>
     <mergeCell ref="A80"/>
+    <mergeCell ref="A22:A25"/>
     <mergeCell ref="A89"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="A50"/>
-    <mergeCell ref="A82:A88"/>
-    <mergeCell ref="A145:A149"/>
-    <mergeCell ref="B145:B149"/>
-    <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B76:B79"/>
-    <mergeCell ref="B125:B126"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="B35:B38"/>
-    <mergeCell ref="B108"/>
+    <mergeCell ref="A26:A33"/>
+    <mergeCell ref="B88"/>
+    <mergeCell ref="B141:B142"/>
+    <mergeCell ref="A53:A58"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="A38:A43"/>
+    <mergeCell ref="A95:A106"/>
+    <mergeCell ref="A90:A94"/>
+    <mergeCell ref="A108:A123"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="A47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/technical-details-consent-technical-details-consent.xlsx
+++ b/generated/spreadsheet/technical-details-consent-technical-details-consent.xlsx
@@ -2184,7 +2184,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">

--- a/generated/spreadsheet/technical-details-consent-technical-details-consent.xlsx
+++ b/generated/spreadsheet/technical-details-consent-technical-details-consent.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I150"/>
+  <dimension ref="A1:I149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -3018,24 +3018,20 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>Building element type</t>
-        </is>
-      </c>
+          <t>Proposal material details</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr"/>
       <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Whether the proposal involves material details that need to be provided</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -3054,24 +3050,24 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Existing materials</t>
+          <t>Building element type</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3085,14 +3081,14 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -3116,19 +3112,19 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Materials not applicable</t>
+          <t>Proposed materials</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Indicates this building element is not relevant to the application</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -3415,7 +3411,8 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -3455,7 +3452,7 @@
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves waste management development</t>
+          <t>Whether the proposal involves any waste management facility that is relevant to the proposal</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -3486,7 +3483,7 @@
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Type of waste management facility</t>
+          <t>Type of waste management facility being described in this entry</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -3510,24 +3507,24 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Total capacity</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Whether the facility is not applicable</t>
+          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3541,24 +3538,24 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Total capacity</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3572,24 +3569,24 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Annual throughput</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Maximum annual operational throughput in tonnes/litres</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3603,24 +3600,24 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Annual throughput</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Maximum annual operational throughput in tonnes/litres</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3629,24 +3626,24 @@
       <c r="B102" s="2" t="n"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
+          <t>Waste streams throughput</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -3665,14 +3662,14 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Construction demolition</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -3696,14 +3693,14 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Construction demolition</t>
+          <t>Commercial industrial</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -3727,14 +3724,14 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Commercial industrial</t>
+          <t>Hazardous</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -3749,82 +3746,82 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n"/>
-      <c r="B106" s="2" t="n"/>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Waste streams throughput</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous</t>
-        </is>
-      </c>
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>What development, works or change of use is proposed</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr"/>
+      <c r="D106" s="2" t="inlineStr"/>
       <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr"/>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Description of the proposal</t>
+          <t>Residential units</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr"/>
+          <t>Details of the residential units that make up both the current and proposed development.</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Residential unit change</t>
+        </is>
+      </c>
       <c r="D107" s="2" t="inlineStr"/>
       <c r="E107" s="2" t="inlineStr"/>
       <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr"/>
-      <c r="I107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Proposal includes the gain, loss or change of use of residential units</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>Residential units</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>Details of the residential units that make up both the current and proposed development.</t>
-        </is>
-      </c>
+      <c r="A108" s="2" t="n"/>
+      <c r="B108" s="2" t="n"/>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Residential unit change</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Tenure type</t>
+        </is>
+      </c>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Proposal includes the gain, loss or change of use of residential units</t>
+          <t>Category of housing tenure</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -3843,14 +3840,14 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Tenure type</t>
+          <t>Housing type</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr"/>
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Category of housing tenure</t>
+          <t>Type of housing</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -3874,19 +3871,23 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Housing type</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr"/>
+          <t>Existing unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Units unknown</t>
+        </is>
+      </c>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Type of housing</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -3910,13 +3911,17 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -3950,22 +3955,22 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Number of bedrooms</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3989,12 +3994,12 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Number of bedrooms</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -4004,7 +4009,7 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4023,17 +4028,13 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -4043,7 +4044,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4057,28 +4058,28 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Existing unit breakdown[]</t>
+          <t>Proposed unit breakdown[]</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Total units</t>
+          <t>Units unknown</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4097,13 +4098,17 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -4137,22 +4142,22 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Number of bedrooms</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4176,12 +4181,12 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Number of bedrooms</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -4191,7 +4196,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4210,17 +4215,13 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -4230,7 +4231,7 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4239,23 +4240,15 @@
       <c r="B120" s="2" t="n"/>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>Proposed unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>Total units</t>
-        </is>
-      </c>
+          <t>Total existing units</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr"/>
+      <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>The total number of existing units</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -4265,7 +4258,7 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4267,7 @@
       <c r="B121" s="2" t="n"/>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Total existing units</t>
+          <t>Total proposed units</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr"/>
@@ -4282,7 +4275,7 @@
       <c r="F121" s="2" t="inlineStr"/>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>The total number of existing units</t>
+          <t>The total number of proposed units</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -4301,7 +4294,7 @@
       <c r="B122" s="2" t="n"/>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Total proposed units</t>
+          <t>Net change</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr"/>
@@ -4309,7 +4302,7 @@
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>The total number of proposed units</t>
+          <t>Calculated net change in units</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -4324,11 +4317,19 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n"/>
-      <c r="B123" s="2" t="n"/>
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Site area</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>How big the site is including relevant measurements</t>
+        </is>
+      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Net change</t>
+          <t>Site area in hectares</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr"/>
@@ -4336,7 +4337,7 @@
       <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Calculated net change in units</t>
+          <t>The size of the site in hectares</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -4351,19 +4352,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>Site area</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>How big the site is including relevant measurements</t>
-        </is>
-      </c>
+      <c r="A124" s="2" t="n"/>
+      <c r="B124" s="2" t="n"/>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Site area in hectares</t>
+          <t>Site area provided by</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr"/>
@@ -4371,39 +4364,51 @@
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>The size of the site in hectares</t>
+          <t>Who provided the site area value</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n"/>
-      <c r="B125" s="2" t="n"/>
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Site area provided by</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Site boundary</t>
+        </is>
+      </c>
       <c r="E125" s="2" t="inlineStr"/>
       <c r="F125" s="2" t="inlineStr"/>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Who provided the site area value</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
@@ -4413,16 +4418,8 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A126" s="2" t="n"/>
+      <c r="B126" s="2" t="n"/>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -4430,19 +4427,19 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
@@ -4461,14 +4458,14 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr"/>
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -4492,19 +4489,19 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr"/>
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
@@ -4523,14 +4520,14 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr"/>
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -4554,14 +4551,14 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr"/>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -4585,14 +4582,14 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr"/>
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -4616,19 +4613,19 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
@@ -4647,14 +4644,14 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr"/>
       <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -4669,50 +4666,46 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n"/>
-      <c r="B134" s="2" t="n"/>
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr"/>
       <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A135" s="2" t="n"/>
+      <c r="B135" s="2" t="n"/>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr"/>
@@ -4720,12 +4713,12 @@
       <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
@@ -4739,7 +4732,7 @@
       <c r="B136" s="2" t="n"/>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr"/>
@@ -4747,17 +4740,17 @@
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4766,15 +4759,19 @@
       <c r="B137" s="2" t="n"/>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="E137" s="2" t="inlineStr"/>
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -4784,7 +4781,7 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4798,14 +4795,14 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -4829,14 +4826,14 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr"/>
       <c r="F139" s="2" t="inlineStr"/>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -4851,28 +4848,32 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n"/>
-      <c r="B140" s="2" t="n"/>
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Trade effluent</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
+        </is>
+      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Disposal required</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr"/>
       <c r="E140" s="2" t="inlineStr"/>
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
@@ -4882,19 +4883,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>Trade effluent</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
-        </is>
-      </c>
+      <c r="A141" s="2" t="n"/>
+      <c r="B141" s="2" t="n"/>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Disposal required</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr"/>
@@ -4902,77 +4895,81 @@
       <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
+          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n"/>
-      <c r="B142" s="2" t="n"/>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Trees and hedges information</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr"/>
       <c r="D142" s="2" t="inlineStr"/>
       <c r="E142" s="2" t="inlineStr"/>
       <c r="F142" s="2" t="inlineStr"/>
-      <c r="G142" s="2" t="inlineStr">
-        <is>
-          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr"/>
+      <c r="I142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Trees and hedges information</t>
+          <t>Vehicle parking</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr"/>
-      <c r="D143" s="2" t="inlineStr"/>
+          <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Parking spaces[]</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Parking space type</t>
+        </is>
+      </c>
       <c r="E143" s="2" t="inlineStr"/>
       <c r="F143" s="2" t="inlineStr"/>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr"/>
-      <c r="I143" s="2" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>Type of parking space or vehicle type</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>Vehicle parking</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
-        </is>
-      </c>
+      <c r="A144" s="2" t="n"/>
+      <c r="B144" s="2" t="n"/>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>Parking spaces[]</t>
@@ -4980,24 +4977,24 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Parking space type</t>
+          <t>Vehicle type other</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr"/>
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Type of parking space or vehicle type</t>
+          <t>Vehicle type when parking space type is 'other'</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5011,24 +5008,24 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Vehicle type other</t>
+          <t>Total existing</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr"/>
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Vehicle type when parking space type is 'other'</t>
+          <t>Total number of existing parking spaces</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5042,14 +5039,14 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Total existing</t>
+          <t>Total proposed</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr"/>
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Total number of existing parking spaces</t>
+          <t>Total number of proposed parking spaces</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -5073,14 +5070,14 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Total proposed</t>
+          <t>Difference in spaces</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr"/>
       <c r="F147" s="2" t="inlineStr"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Total number of proposed parking spaces</t>
+          <t>Net change in parking spaces (proposed minus existing)</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -5095,50 +5092,46 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n"/>
-      <c r="B148" s="2" t="n"/>
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Waste storage and collection</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
+        </is>
+      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Parking spaces[]</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>Difference in spaces</t>
-        </is>
-      </c>
+          <t>Waste storage area details</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr"/>
       <c r="E148" s="2" t="inlineStr"/>
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Net change in parking spaces (proposed minus existing)</t>
+          <t>Details of the waste storage area including location, size, design and access arrangements</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>Waste storage and collection</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
-        </is>
-      </c>
+      <c r="A149" s="2" t="n"/>
+      <c r="B149" s="2" t="n"/>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Waste storage area details</t>
+          <t>Separate recycling arrangements details</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr"/>
@@ -5146,7 +5139,7 @@
       <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Details of the waste storage area including location, size, design and access arrangements</t>
+          <t>Details of the recycling arrangements including types of materials, collection methods and storage facilities</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -5155,33 +5148,6 @@
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="n"/>
-      <c r="B150" s="2" t="n"/>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>Separate recycling arrangements details</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr"/>
-      <c r="E150" s="2" t="inlineStr"/>
-      <c r="F150" s="2" t="inlineStr"/>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t>Details of the recycling arrangements including types of materials, collection methods and storage facilities</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I150" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
@@ -5191,64 +5157,64 @@
   <mergeCells count="62">
     <mergeCell ref="B22:B25"/>
     <mergeCell ref="B49"/>
-    <mergeCell ref="B149:B150"/>
+    <mergeCell ref="B140:B141"/>
     <mergeCell ref="B75:B78"/>
-    <mergeCell ref="B135:B140"/>
-    <mergeCell ref="B143"/>
+    <mergeCell ref="A106"/>
     <mergeCell ref="B26:B33"/>
-    <mergeCell ref="A149:A150"/>
+    <mergeCell ref="B134:B139"/>
+    <mergeCell ref="B148:B149"/>
     <mergeCell ref="B89"/>
+    <mergeCell ref="B142"/>
     <mergeCell ref="A59:A68"/>
     <mergeCell ref="B80"/>
     <mergeCell ref="B59:B68"/>
-    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="A95:A105"/>
     <mergeCell ref="B79"/>
     <mergeCell ref="B2:B18"/>
     <mergeCell ref="A44:A46"/>
     <mergeCell ref="A81:A87"/>
-    <mergeCell ref="A144:A148"/>
-    <mergeCell ref="B95:B106"/>
+    <mergeCell ref="B143:B147"/>
     <mergeCell ref="A75:A78"/>
-    <mergeCell ref="A126:A134"/>
     <mergeCell ref="A48"/>
-    <mergeCell ref="A143"/>
-    <mergeCell ref="B108:B123"/>
+    <mergeCell ref="A123:A124"/>
     <mergeCell ref="A69:A74"/>
+    <mergeCell ref="B106"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="B47"/>
+    <mergeCell ref="A143:A147"/>
     <mergeCell ref="A49"/>
-    <mergeCell ref="A107"/>
     <mergeCell ref="B38:B43"/>
+    <mergeCell ref="A125:A133"/>
+    <mergeCell ref="A142"/>
     <mergeCell ref="B50:B52"/>
     <mergeCell ref="A79"/>
     <mergeCell ref="A88"/>
-    <mergeCell ref="A141:A142"/>
-    <mergeCell ref="B144:B148"/>
-    <mergeCell ref="B126:B134"/>
     <mergeCell ref="B48"/>
     <mergeCell ref="B34:B37"/>
     <mergeCell ref="B69:B74"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="A107:A122"/>
     <mergeCell ref="A2:A18"/>
-    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="B95:B105"/>
     <mergeCell ref="B90:B94"/>
-    <mergeCell ref="A135:A140"/>
     <mergeCell ref="B81:B87"/>
-    <mergeCell ref="B107"/>
     <mergeCell ref="A50:A52"/>
     <mergeCell ref="B53:B58"/>
+    <mergeCell ref="B123:B124"/>
     <mergeCell ref="A80"/>
     <mergeCell ref="A22:A25"/>
+    <mergeCell ref="B125:B133"/>
+    <mergeCell ref="A134:A139"/>
     <mergeCell ref="A89"/>
     <mergeCell ref="A26:A33"/>
     <mergeCell ref="B88"/>
-    <mergeCell ref="B141:B142"/>
     <mergeCell ref="A53:A58"/>
     <mergeCell ref="A34:A37"/>
     <mergeCell ref="B44:B46"/>
     <mergeCell ref="A38:A43"/>
-    <mergeCell ref="A95:A106"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="B107:B122"/>
     <mergeCell ref="A90:A94"/>
-    <mergeCell ref="A108:A123"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="A47"/>
   </mergeCells>

--- a/generated/spreadsheet/technical-details-consent-technical-details-consent.xlsx
+++ b/generated/spreadsheet/technical-details-consent-technical-details-consent.xlsx
@@ -427,17 +427,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I149"/>
+  <dimension ref="A1:I211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -491,29 +491,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Submission reference</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A unique reference for the submission</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -532,7 +532,7 @@
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -563,19 +563,19 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Specification profile</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>The specification profile used to determine context-specific allowed codelist values for the application</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -594,24 +594,24 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -625,24 +625,24 @@
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
+          <t>Submitted at</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>The date and time the application was submitted</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -656,28 +656,24 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Created at</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The date and time the submission payload was created</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -691,7 +687,7 @@
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -701,13 +697,13 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -726,7 +722,7 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -736,13 +732,13 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -752,7 +748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -761,7 +757,7 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -771,23 +767,23 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -796,7 +792,7 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -806,18 +802,18 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -831,7 +827,7 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -841,27 +837,23 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Base64</t>
-        </is>
-      </c>
+          <t>Uploaded date</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -870,7 +862,7 @@
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -885,12 +877,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>Base64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -900,7 +892,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -909,7 +901,7 @@
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -924,12 +916,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -939,7 +931,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -948,7 +940,7 @@
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -963,17 +955,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>File size</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -987,33 +979,37 @@
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Fee</t>
+          <t>Documents[]</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>File size</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1018,7 @@
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1032,18 +1028,18 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1057,7 +1053,7 @@
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1067,67 +1063,75 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Transactions[]</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Access and rights of way</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>New or altered vehicle access</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="2" t="inlineStr"/>
+          <t>Submission details</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Fee</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Transactions[]</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Access and rights of way</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>New or altered pedestrian access</t>
+          <t>New or altered vehicle access</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
@@ -1135,7 +1139,7 @@
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
+          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1154,24 +1158,20 @@
       <c r="B21" s="2" t="n"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>New or altered pedestrian access</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1181,19 +1181,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
+          <t>Change to right of way</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
@@ -1201,12 +1193,12 @@
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>Will the proposal change public rights of way (diversion/extinguishment/creation)</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1220,24 +1212,20 @@
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>New right of way</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Will new public rights of way be provided within or adjacent to the site</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1251,33 +1239,25 @@
       <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>New public road</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>Will new public roads be provided within the site</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1286,40 +1266,36 @@
       <c r="B25" s="2" t="n"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Supporting documents[]</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Agent details</t>
+          <t>Agent contact details</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1329,19 +1305,15 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1351,7 +1323,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1360,23 +1332,19 @@
       <c r="B27" s="2" t="n"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1386,7 +1354,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1395,23 +1363,23 @@
       <c r="B28" s="2" t="n"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>Phone number(s)[]</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1421,7 +1389,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1430,39 +1398,47 @@
       <c r="B29" s="2" t="n"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>Phone number(s)[]</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n"/>
-      <c r="B30" s="2" t="n"/>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>agent</t>
@@ -1470,18 +1446,14 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1510,13 +1482,13 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1540,14 +1512,18 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>First Name</t>
+        </is>
+      </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1557,7 +1533,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1571,49 +1547,53 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Last Name</t>
+        </is>
+      </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="n"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1632,19 +1612,23 @@
       <c r="B35" s="2" t="n"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1654,7 +1638,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1663,23 +1647,19 @@
       <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1698,23 +1678,19 @@
       <c r="B37" s="2" t="n"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>User role</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1731,29 +1707,25 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Applicant details</t>
+          <t>Applicant contact details</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1772,23 +1744,19 @@
       <c r="B39" s="2" t="n"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1798,7 +1766,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1807,23 +1775,23 @@
       <c r="B40" s="2" t="n"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>Phone number(s)[]</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1833,7 +1801,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1842,39 +1810,47 @@
       <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>Phone number(s)[]</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n"/>
-      <c r="B42" s="2" t="n"/>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1882,18 +1858,14 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -1922,13 +1894,13 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -1943,32 +1915,32 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity, geological and archaeological conservation</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="n"/>
+      <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Protected species impact</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>First Name</t>
+        </is>
+      </c>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of protected and priority species being affected?</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -1982,20 +1954,28 @@
       <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity features impact</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr"/>
-      <c r="E45" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Last Name</t>
+        </is>
+      </c>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2009,20 +1989,28 @@
       <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Geological features impact</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr"/>
-      <c r="E46" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2032,38 +2020,54 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity net gain</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr"/>
-      <c r="D47" s="2" t="inlineStr"/>
-      <c r="E47" s="2" t="inlineStr"/>
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>The postal code</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Biodiversity, geological and archaeological conservation</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Protected species impact</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -2071,12 +2075,12 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Where is there a likelihood of protected and priority species being affected?</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2086,38 +2090,38 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr"/>
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity features impact</t>
+        </is>
+      </c>
       <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Geological features impact</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -2125,12 +2129,12 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2140,11 +2144,19 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n"/>
-      <c r="B51" s="2" t="n"/>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity net gain</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
+        </is>
+      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Biodiversity gain condition applies</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -2152,7 +2164,7 @@
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2171,20 +2183,24 @@
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr"/>
+          <t>Biodiversity gain condition exemption reason[]</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Exemption type</t>
+        </is>
+      </c>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2194,36 +2210,28 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>How the proposed development will impact existing and proposed employee numbers</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="n"/>
+      <c r="B53" s="2" t="n"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
+          <t>Biodiversity gain condition exemption reason[]</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>The reason the exemption applies to this proposal</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2237,24 +2245,24 @@
       <c r="B54" s="2" t="n"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
+          <t>Biodiversity net gain details</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Pre development date</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2268,24 +2276,24 @@
       <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
+          <t>Biodiversity net gain details</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Pre development biodiversity value</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2299,29 +2307,29 @@
       <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Biodiversity net gain details</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Earlier date reason</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Reason for using a pre-development date that is earlier than the application submission</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2330,29 +2338,29 @@
       <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Biodiversity net gain details</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Habitat loss after 2020</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2361,24 +2369,28 @@
       <c r="B58" s="2" t="n"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Biodiversity net gain details</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Loss date</t>
+        </is>
+      </c>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Date the activity causing habitat loss or degradation occurred</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -2388,36 +2400,32 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Existing use</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>How the site is currently being used.</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="n"/>
+      <c r="B59" s="2" t="n"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
+          <t>Biodiversity net gain details</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Pre loss biodiversity value</t>
+        </is>
+      </c>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -2431,19 +2439,23 @@
       <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
+          <t>Biodiversity net gain details</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Use details</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Supporting evidence</t>
+        </is>
+      </c>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Further detail of the use</t>
+          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2462,24 +2474,24 @@
       <c r="B61" s="2" t="n"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
+          <t>Biodiversity net gain details</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Land part</t>
+          <t>Metric publication date</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Which part of the land the use relates to</t>
+          <t>Publication date of the biodiversity metric tool used for calculations</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -2493,15 +2505,19 @@
       <c r="B62" s="2" t="n"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Site vacant</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr"/>
+          <t>Biodiversity net gain details</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Irreplaceable habitats</t>
+        </is>
+      </c>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Is the site currently vacant</t>
+          <t>Indicates whether the site contains any irreplaceable habitats</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -2520,15 +2536,19 @@
       <c r="B63" s="2" t="n"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Last use details</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr"/>
+          <t>Biodiversity net gain details</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Irreplaceable habitats details</t>
+        </is>
+      </c>
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Description of the last use of the site</t>
+          <t>Description and references for any irreplaceable habitats identified on the site</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -2547,34 +2567,50 @@
       <c r="B64" s="2" t="n"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Last use end date</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr"/>
-      <c r="E64" s="2" t="inlineStr"/>
+          <t>Biodiversity net gain details</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Date the last use ended (YYYY-MM-DD format)</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n"/>
-      <c r="B65" s="2" t="n"/>
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+        </is>
+      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Is contaminated land</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
@@ -2582,12 +2618,12 @@
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Is the site known to be contaminated?</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -2597,11 +2633,19 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n"/>
-      <c r="B66" s="2" t="n"/>
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Is suspected contaminated land</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
@@ -2609,7 +2653,7 @@
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Is the site suspected of contamination?</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -2628,7 +2672,7 @@
       <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Proposed use contamination risk</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
@@ -2636,17 +2680,17 @@
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Is the proposed use vulnerable to the presence of contamination?</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2699,7 @@
       <c r="B68" s="2" t="n"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Contamination assessment</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
@@ -2663,7 +2707,7 @@
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Reference to contamination assessment document</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -2680,17 +2724,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Flood risk assessment</t>
+          <t>Declaration</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Results of any flood risk assessments made for the development site</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Flood risk area</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
@@ -2698,12 +2742,12 @@
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Is the site within an area at risk of flooding?</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -2717,7 +2761,7 @@
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Data provided by</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
@@ -2725,17 +2769,17 @@
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Who provided the data: Applicant or System/Service?</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2788,7 @@
       <c r="B71" s="2" t="n"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Flood risk assessment</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
@@ -2752,39 +2796,51 @@
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Reference of the flood risk assessment document</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n"/>
-      <c r="B72" s="2" t="n"/>
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>How the proposed development will impact existing and proposed employee numbers</t>
+        </is>
+      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Within 20m watercourse</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr"/>
+          <t>Existing employees</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Whether the development is within 20 metres of a watercourse</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -2798,20 +2854,24 @@
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Increases flood risk</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr"/>
+          <t>Existing employees</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Part-time</t>
+        </is>
+      </c>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Whether the development increases flood risk</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -2825,20 +2885,24 @@
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Surface water disposal[]</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr"/>
+          <t>Existing employees</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Total FTE</t>
+        </is>
+      </c>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Method for disposing of surface water</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -2848,32 +2912,28 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>Foul sewage disposal</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>How waste water will leave the property as part of the proposed development</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="n"/>
+      <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Has new disposal arrangements</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr"/>
+          <t>Proposed employees</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include any new foul sewage disposal arrangments</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -2887,25 +2947,29 @@
       <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Foul sewage disposal types[]</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr"/>
+          <t>Proposed employees</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Part-time</t>
+        </is>
+      </c>
       <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>List of ways foul sewage will be disposed of</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2914,20 +2978,24 @@
       <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Connect to drainage system</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr"/>
+          <t>Proposed employees</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Total FTE</t>
+        </is>
+      </c>
       <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal needs to connect to the existing drainage system</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -2937,28 +3005,36 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n"/>
-      <c r="B78" s="2" t="n"/>
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Existing use</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>How the site is currently being used.</t>
+        </is>
+      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
+          <t>Existing use details[]</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -2968,57 +3044,73 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous substances</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>Details of hazardous substances requiring consent used as part of the development</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr"/>
-      <c r="D79" s="2" t="inlineStr"/>
+      <c r="A79" s="2" t="n"/>
+      <c r="B79" s="2" t="n"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Existing use details[]</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Use details</t>
+        </is>
+      </c>
       <c r="E79" s="2" t="inlineStr"/>
       <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Further detail of the use</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>Hours of operation</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr"/>
-      <c r="D80" s="2" t="inlineStr"/>
+      <c r="A80" s="2" t="n"/>
+      <c r="B80" s="2" t="n"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Existing use details[]</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Land part</t>
+        </is>
+      </c>
       <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Which part of the land the use relates to</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>What materials are being used for the proposed development</t>
-        </is>
-      </c>
+      <c r="A81" s="2" t="n"/>
+      <c r="B81" s="2" t="n"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Proposal material details</t>
+          <t>Site vacant</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
@@ -3026,7 +3118,7 @@
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves material details that need to be provided</t>
+          <t>Is the site currently vacant</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -3045,29 +3137,25 @@
       <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>Building element type</t>
-        </is>
-      </c>
+          <t>Last use details</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr"/>
       <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Description of the last use of the site</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3076,24 +3164,20 @@
       <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Existing materials</t>
-        </is>
-      </c>
+          <t>Last use end date</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" s="2" t="inlineStr"/>
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>Date the last use ended (YYYY-MM-DD format)</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -3107,29 +3191,25 @@
       <c r="B84" s="2" t="n"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Proposed materials</t>
-        </is>
-      </c>
+          <t>Is contaminated land</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>Is the site known to be contaminated?</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3138,19 +3218,15 @@
       <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Materials not known</t>
-        </is>
-      </c>
+          <t>Is suspected contaminated land</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Indicates the materials for this building element are not yet known</t>
+          <t>Is the site suspected of contamination?</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -3160,7 +3236,7 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3245,7 @@
       <c r="B86" s="2" t="n"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Providing additional material information</t>
+          <t>Proposed use contamination risk</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
@@ -3177,7 +3253,7 @@
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
+          <t>Is the proposed use vulnerable to the presence of contamination?</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -3196,19 +3272,15 @@
       <c r="B87" s="2" t="n"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Contamination assessment</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Reference to contamination assessment document</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -3218,62 +3290,78 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Non residential floorspace</t>
+          <t>Flood risk assessment</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Details of changes to non-residential floorspace in the proposed development.</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr"/>
+          <t>Results of any flood risk assessments made for the development site</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Flood risk area</t>
+        </is>
+      </c>
       <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Is the site within an area at risk of flooding?</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr"/>
+      <c r="A89" s="2" t="n"/>
+      <c r="B89" s="2" t="n"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Data provided by</t>
+        </is>
+      </c>
       <c r="D89" s="2" t="inlineStr"/>
       <c r="E89" s="2" t="inlineStr"/>
       <c r="F89" s="2" t="inlineStr"/>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr"/>
-      <c r="I89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Who provided the data: Applicant or System/Service?</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A90" s="2" t="n"/>
+      <c r="B90" s="2" t="n"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Flood risk assessment</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
@@ -3281,17 +3369,17 @@
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Reference of the flood risk assessment document</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3388,7 @@
       <c r="B91" s="2" t="n"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Within 20m watercourse</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
@@ -3308,17 +3396,17 @@
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Whether the development is within 20 metres of a watercourse</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3327,7 +3415,7 @@
       <c r="B92" s="2" t="n"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Increases flood risk</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr"/>
@@ -3335,17 +3423,17 @@
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Whether the development increases flood risk</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3442,7 @@
       <c r="B93" s="2" t="n"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Surface water disposal[]</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
@@ -3362,26 +3450,34 @@
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Method for disposing of surface water</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n"/>
-      <c r="B94" s="2" t="n"/>
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Foul sewage disposal</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>How waste water will leave the property as part of the proposed development</t>
+        </is>
+      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Has new disposal arrangements</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
@@ -3389,35 +3485,26 @@
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Does the proposal include any new foul sewage disposal arrangments</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>Processes machinery waste</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">How waste will be managed on the site
-</t>
-        </is>
-      </c>
+      <c r="A95" s="2" t="n"/>
+      <c r="B95" s="2" t="n"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Site activity details</t>
+          <t>Foul sewage disposal types[]</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
@@ -3425,17 +3512,17 @@
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
+          <t>List of ways foul sewage will be disposed of</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3531,7 @@
       <c r="B96" s="2" t="n"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Proposal waste management</t>
+          <t>Connect to drainage system</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
@@ -3452,7 +3539,7 @@
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves any waste management facility that is relevant to the proposal</t>
+          <t>Whether the proposal needs to connect to the existing drainage system</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -3471,24 +3558,24 @@
       <c r="B97" s="2" t="n"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
+          <t>Supporting documents[]</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Waste management facility type</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Type of waste management facility being described in this entry</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -3498,28 +3585,32 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n"/>
-      <c r="B98" s="2" t="n"/>
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Hazardous substances</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Details of hazardous substances requiring consent used as part of the development</t>
+        </is>
+      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>Total capacity</t>
-        </is>
-      </c>
+          <t>Involves hazardous substances</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr"/>
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
+          <t>Indicates if hazardous substances are involved in the proposal</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -3533,19 +3624,19 @@
       <c r="B99" s="2" t="n"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
+          <t>Substance types[]</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Hazardous substance type</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Reference of hazardous substance type from predefined list</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -3564,29 +3655,29 @@
       <c r="B100" s="2" t="n"/>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
+          <t>Substance types[]</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Annual throughput</t>
+          <t>Hazardous substance other</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Maximum annual operational throughput in tonnes/litres</t>
+          <t>The specific name of the hazardous substance if other is selected</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3595,24 +3686,24 @@
       <c r="B101" s="2" t="n"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
+          <t>Substance types[]</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -3622,33 +3713,41 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n"/>
-      <c r="B102" s="2" t="n"/>
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Hours of operation</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
+        </is>
+      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
+          <t>Hours of operation[]</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3657,24 +3756,24 @@
       <c r="B103" s="2" t="n"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
+          <t>Hours of operation[]</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Construction demolition</t>
+          <t>Use other</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -3688,29 +3787,33 @@
       <c r="B104" s="2" t="n"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
+          <t>Hours of operation[]</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Commercial industrial</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr"/>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Schedule days[]</t>
+        </is>
+      </c>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
+          <t>List of days or day categories that a schedule entry applies to</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3719,24 +3822,28 @@
       <c r="B105" s="2" t="n"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
+          <t>Hours of operation[]</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Hazardous</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr"/>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
+          <t>True or False - explicitly state when closed</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -3746,51 +3853,75 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>What development, works or change of use is proposed</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr"/>
-      <c r="D106" s="2" t="inlineStr"/>
-      <c r="E106" s="2" t="inlineStr"/>
-      <c r="F106" s="2" t="inlineStr"/>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr"/>
-      <c r="I106" s="2" t="inlineStr"/>
+      <c r="A106" s="2" t="n"/>
+      <c r="B106" s="2" t="n"/>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Hours of operation[]</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Open time</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Opening time</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>Residential units</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>Details of the residential units that make up both the current and proposed development.</t>
-        </is>
-      </c>
+      <c r="A107" s="2" t="n"/>
+      <c r="B107" s="2" t="n"/>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Residential unit change</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr"/>
-      <c r="E107" s="2" t="inlineStr"/>
-      <c r="F107" s="2" t="inlineStr"/>
+          <t>Hours of operation[]</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Close time</t>
+        </is>
+      </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Proposal includes the gain, loss or change of use of residential units</t>
+          <t>Closing time</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -3804,55 +3935,59 @@
       <c r="B108" s="2" t="n"/>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
+          <t>Hours of operation[]</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Tenure type</t>
+          <t>Hours not known</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Category of housing tenure</t>
+          <t>Applicant states they do not know the hours of operation</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n"/>
-      <c r="B109" s="2" t="n"/>
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>What materials are being used for the proposed development</t>
+        </is>
+      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>Housing type</t>
-        </is>
-      </c>
+          <t>Proposal material details</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr"/>
       <c r="E109" s="2" t="inlineStr"/>
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Type of housing</t>
+          <t>Whether the proposal involves material details that need to be provided</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -3866,28 +4001,24 @@
       <c r="B110" s="2" t="n"/>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
+          <t>Building elements[]</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Existing unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
+          <t>Building element type</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -3901,37 +4032,29 @@
       <c r="B111" s="2" t="n"/>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
+          <t>Building elements[]</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Existing unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>No bedrooms unknown</t>
-        </is>
-      </c>
+          <t>Existing materials</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr"/>
+      <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3940,32 +4063,24 @@
       <c r="B112" s="2" t="n"/>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
+          <t>Building elements[]</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Existing unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>Number of bedrooms</t>
-        </is>
-      </c>
+          <t>Proposed materials</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
@@ -3979,37 +4094,29 @@
       <c r="B113" s="2" t="n"/>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
+          <t>Building elements[]</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Existing unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Materials not known</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr"/>
+      <c r="F113" s="2" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Indicates the materials for this building element are not yet known</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4018,33 +4125,25 @@
       <c r="B114" s="2" t="n"/>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>Existing unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>Total units</t>
-        </is>
-      </c>
+          <t>Providing additional material information</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr"/>
+      <c r="E114" s="2" t="inlineStr"/>
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4053,28 +4152,24 @@
       <c r="B115" s="2" t="n"/>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
+          <t>Supporting documents[]</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Proposed unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr"/>
       <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
@@ -4084,31 +4179,27 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n"/>
-      <c r="B116" s="2" t="n"/>
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Non residential floorspace</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Details of changes to non-residential floorspace in the proposed development.</t>
+        </is>
+      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>Proposed unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>No bedrooms unknown</t>
-        </is>
-      </c>
+          <t>Non residential change</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr"/>
+      <c r="E116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -4127,37 +4218,29 @@
       <c r="B117" s="2" t="n"/>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
+          <t>Floorspace details[]</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Proposed unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>Number of bedrooms</t>
-        </is>
-      </c>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr"/>
+      <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4166,37 +4249,29 @@
       <c r="B118" s="2" t="n"/>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
+          <t>Floorspace details[]</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Proposed unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Specified use</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>A specified use if no applicable use class is available</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4205,33 +4280,29 @@
       <c r="B119" s="2" t="n"/>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
+          <t>Floorspace details[]</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Proposed unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>Total units</t>
-        </is>
-      </c>
+          <t>Existing gross floorspace</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr"/>
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>Existing gross internal floorspace, in sqm</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4240,20 +4311,24 @@
       <c r="B120" s="2" t="n"/>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Total existing units</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr"/>
+          <t>Floorspace details[]</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Floorspace lost</t>
+        </is>
+      </c>
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>The total number of existing units</t>
+          <t>Gross floorspace to be lost by change of use, in sqm</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
@@ -4267,20 +4342,24 @@
       <c r="B121" s="2" t="n"/>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Total proposed units</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr"/>
+          <t>Floorspace details[]</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Total gross proposed</t>
+        </is>
+      </c>
       <c r="E121" s="2" t="inlineStr"/>
       <c r="F121" s="2" t="inlineStr"/>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>The total number of proposed units</t>
+          <t>Total gross internal floorspace proposed, in sqm</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
@@ -4294,20 +4373,24 @@
       <c r="B122" s="2" t="n"/>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Net change</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr"/>
+          <t>Floorspace details[]</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Net additional floorspace</t>
+        </is>
+      </c>
       <c r="E122" s="2" t="inlineStr"/>
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Calculated net change in units</t>
+          <t>Net additional gross internal floorspace, in sqm</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
@@ -4317,32 +4400,28 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>Site area</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>How big the site is including relevant measurements</t>
-        </is>
-      </c>
+      <c r="A123" s="2" t="n"/>
+      <c r="B123" s="2" t="n"/>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Site area in hectares</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr"/>
+          <t>Room details[]</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Use class for accommodation</t>
+        </is>
+      </c>
       <c r="E123" s="2" t="inlineStr"/>
       <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>The size of the site in hectares</t>
+          <t>Type of non-residential use class referring to accommodation uses</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
@@ -4356,20 +4435,24 @@
       <c r="B124" s="2" t="n"/>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Site area provided by</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr"/>
+          <t>Room details[]</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Use other</t>
+        </is>
+      </c>
       <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Who provided the site area value</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
@@ -4379,41 +4462,33 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A125" s="2" t="n"/>
+      <c r="B125" s="2" t="n"/>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Room details[]</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Existing rooms lost</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
       <c r="F125" s="2" t="inlineStr"/>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Existing rooms to be lost by change of use</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4422,29 +4497,29 @@
       <c r="B126" s="2" t="n"/>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Room details[]</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Total rooms proposed</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Total rooms proposed (including change of use)</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4453,60 +4528,64 @@
       <c r="B127" s="2" t="n"/>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Room details[]</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Net additional rooms</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr"/>
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Net additional rooms following development</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n"/>
-      <c r="B128" s="2" t="n"/>
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+        </is>
+      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>Easting</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr"/>
       <c r="E128" s="2" t="inlineStr"/>
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4515,29 +4594,25 @@
       <c r="B129" s="2" t="n"/>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>Northing</t>
-        </is>
-      </c>
+          <t>Agricultural tenants</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr"/>
       <c r="E129" s="2" t="inlineStr"/>
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4546,24 +4621,28 @@
       <c r="B130" s="2" t="n"/>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Owners and tenants[]</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
@@ -4577,29 +4656,33 @@
       <c r="B131" s="2" t="n"/>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Owners and tenants[]</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>First Name</t>
+        </is>
+      </c>
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4608,19 +4691,23 @@
       <c r="B132" s="2" t="n"/>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Owners and tenants[]</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Last Name</t>
+        </is>
+      </c>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -4630,7 +4717,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4639,19 +4726,23 @@
       <c r="B133" s="2" t="n"/>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Owners and tenants[]</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -4661,42 +4752,42 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A134" s="2" t="n"/>
+      <c r="B134" s="2" t="n"/>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr"/>
-      <c r="E134" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4705,25 +4796,29 @@
       <c r="B135" s="2" t="n"/>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Notice served date</t>
+        </is>
+      </c>
       <c r="E135" s="2" t="inlineStr"/>
       <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4732,7 +4827,7 @@
       <c r="B136" s="2" t="n"/>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
+          <t>Ownership certificate type</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr"/>
@@ -4740,12 +4835,12 @@
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
@@ -4759,19 +4854,15 @@
       <c r="B137" s="2" t="n"/>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Steps taken</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr"/>
       <c r="E137" s="2" t="inlineStr"/>
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -4781,7 +4872,7 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4790,19 +4881,19 @@
       <c r="B138" s="2" t="n"/>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
+          <t>Newspaper notices[]</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Newspaper name</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -4821,24 +4912,24 @@
       <c r="B139" s="2" t="n"/>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
+          <t>Newspaper notices[]</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Publication date</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr"/>
       <c r="F139" s="2" t="inlineStr"/>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
@@ -4848,19 +4939,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>Trade effluent</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
-        </is>
-      </c>
+      <c r="A140" s="2" t="n"/>
+      <c r="B140" s="2" t="n"/>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Disposal required</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr"/>
@@ -4868,12 +4951,12 @@
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
@@ -4887,7 +4970,7 @@
       <c r="B141" s="2" t="n"/>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr"/>
@@ -4895,70 +4978,74 @@
       <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>Trees and hedges information</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr"/>
+      <c r="A142" s="2" t="n"/>
+      <c r="B142" s="2" t="n"/>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Declaration date</t>
+        </is>
+      </c>
       <c r="D142" s="2" t="inlineStr"/>
       <c r="E142" s="2" t="inlineStr"/>
       <c r="F142" s="2" t="inlineStr"/>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr"/>
-      <c r="I142" s="2" t="inlineStr"/>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>The date the declaration was made</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Vehicle parking</t>
+          <t>Pre-application advice</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Parking spaces[]</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
-        <is>
-          <t>Parking space type</t>
-        </is>
-      </c>
+          <t>Pre-application advice sought</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr"/>
       <c r="E143" s="2" t="inlineStr"/>
       <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Type of parking space or vehicle type</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
@@ -4972,19 +5059,15 @@
       <c r="B144" s="2" t="n"/>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Parking spaces[]</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>Vehicle type other</t>
-        </is>
-      </c>
+          <t>Officer name</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr"/>
       <c r="E144" s="2" t="inlineStr"/>
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Vehicle type when parking space type is 'other'</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -5003,29 +5086,25 @@
       <c r="B145" s="2" t="n"/>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Parking spaces[]</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>Total existing</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr"/>
       <c r="E145" s="2" t="inlineStr"/>
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Total number of existing parking spaces</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5034,29 +5113,25 @@
       <c r="B146" s="2" t="n"/>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Parking spaces[]</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>Total proposed</t>
-        </is>
-      </c>
+          <t>Advice date</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr"/>
       <c r="E146" s="2" t="inlineStr"/>
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Total number of proposed parking spaces</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5065,46 +5140,43 @@
       <c r="B147" s="2" t="n"/>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Parking spaces[]</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>Difference in spaces</t>
-        </is>
-      </c>
+          <t>Advice summary</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr"/>
       <c r="E147" s="2" t="inlineStr"/>
       <c r="F147" s="2" t="inlineStr"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Net change in parking spaces (proposed minus existing)</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Waste storage and collection</t>
+          <t>Processes machinery waste</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Waste storage area details</t>
+          <t>Site activity details</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr"/>
@@ -5112,7 +5184,7 @@
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Details of the waste storage area including location, size, design and access arrangements</t>
+          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -5122,7 +5194,7 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5131,7 +5203,7 @@
       <c r="B149" s="2" t="n"/>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Separate recycling arrangements details</t>
+          <t>Proposal waste management</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr"/>
@@ -5139,15 +5211,1977 @@
       <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
+          <t>Whether the proposal involves any waste management facility that is relevant to the proposal</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n"/>
+      <c r="B150" s="2" t="n"/>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Waste management[]</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Waste management facility type</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr"/>
+      <c r="F150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>Type of waste management facility being described in this entry</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n"/>
+      <c r="B151" s="2" t="n"/>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Waste management[]</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Total capacity</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr"/>
+      <c r="F151" s="2" t="inlineStr"/>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n"/>
+      <c r="B152" s="2" t="n"/>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Waste management[]</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Unit type</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr"/>
+      <c r="F152" s="2" t="inlineStr"/>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n"/>
+      <c r="B153" s="2" t="n"/>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Waste management[]</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Annual throughput</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr"/>
+      <c r="F153" s="2" t="inlineStr"/>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>Maximum annual operational throughput in tonnes/litres</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n"/>
+      <c r="B154" s="2" t="n"/>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Waste management[]</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Unit type</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr"/>
+      <c r="F154" s="2" t="inlineStr"/>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n"/>
+      <c r="B155" s="2" t="n"/>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Waste streams throughput</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr"/>
+      <c r="F155" s="2" t="inlineStr"/>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n"/>
+      <c r="B156" s="2" t="n"/>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Waste streams throughput</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Construction demolition</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr"/>
+      <c r="F156" s="2" t="inlineStr"/>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n"/>
+      <c r="B157" s="2" t="n"/>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Waste streams throughput</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Commercial industrial</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr"/>
+      <c r="F157" s="2" t="inlineStr"/>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n"/>
+      <c r="B158" s="2" t="n"/>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Waste streams throughput</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Hazardous</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr"/>
+      <c r="F158" s="2" t="inlineStr"/>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>What development, works or change of use is proposed</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Proposal description</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr"/>
+      <c r="E159" s="2" t="inlineStr"/>
+      <c r="F159" s="2" t="inlineStr"/>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n"/>
+      <c r="B160" s="2" t="n"/>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Proposal started</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr"/>
+      <c r="E160" s="2" t="inlineStr"/>
+      <c r="F160" s="2" t="inlineStr"/>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>Has any work on the proposal already been started</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n"/>
+      <c r="B161" s="2" t="n"/>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Proposal start date</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr"/>
+      <c r="E161" s="2" t="inlineStr"/>
+      <c r="F161" s="2" t="inlineStr"/>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n"/>
+      <c r="B162" s="2" t="n"/>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Proposal completed</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr"/>
+      <c r="E162" s="2" t="inlineStr"/>
+      <c r="F162" s="2" t="inlineStr"/>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>Has any work on the proposal already been completed</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n"/>
+      <c r="B163" s="2" t="n"/>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Proposal completion date</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr"/>
+      <c r="E163" s="2" t="inlineStr"/>
+      <c r="F163" s="2" t="inlineStr"/>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n"/>
+      <c r="B164" s="2" t="n"/>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>PIP reference</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr"/>
+      <c r="E164" s="2" t="inlineStr"/>
+      <c r="F164" s="2" t="inlineStr"/>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>Reference number for the Planning in Principle (PIP) application this relates to</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n"/>
+      <c r="B165" s="2" t="n"/>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Is public service infrastructure</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr"/>
+      <c r="E165" s="2" t="inlineStr"/>
+      <c r="F165" s="2" t="inlineStr"/>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>For applications made on or after 1 August 2021, is the proposal for public service infrastructure development</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Residential units</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Details of the residential units that make up both the current and proposed development.</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Residential unit change</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr"/>
+      <c r="E166" s="2" t="inlineStr"/>
+      <c r="F166" s="2" t="inlineStr"/>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Proposal includes the gain, loss or change of use of residential units</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n"/>
+      <c r="B167" s="2" t="n"/>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Tenure type</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr"/>
+      <c r="F167" s="2" t="inlineStr"/>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>Category of housing tenure</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n"/>
+      <c r="B168" s="2" t="n"/>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Housing type</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr"/>
+      <c r="F168" s="2" t="inlineStr"/>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>Type of housing</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n"/>
+      <c r="B169" s="2" t="n"/>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Existing unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>Units unknown</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr"/>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>Whether the number of units is unknown</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n"/>
+      <c r="B170" s="2" t="n"/>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Existing unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Set to true when counting units where bedroom number is unknown</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n"/>
+      <c r="B171" s="2" t="n"/>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Existing unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>Number of bedrooms</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>The number of bedrooms in unit</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n"/>
+      <c r="B172" s="2" t="n"/>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Existing unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>The number of units of that bedroom count</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n"/>
+      <c r="B173" s="2" t="n"/>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Existing unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr"/>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Total number of units</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n"/>
+      <c r="B174" s="2" t="n"/>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Proposed unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Units unknown</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr"/>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>Whether the number of units is unknown</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n"/>
+      <c r="B175" s="2" t="n"/>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Proposed unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>Set to true when counting units where bedroom number is unknown</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n"/>
+      <c r="B176" s="2" t="n"/>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Proposed unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Number of bedrooms</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>The number of bedrooms in unit</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n"/>
+      <c r="B177" s="2" t="n"/>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Proposed unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>The number of units of that bedroom count</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n"/>
+      <c r="B178" s="2" t="n"/>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Proposed unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr"/>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>Total number of units</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n"/>
+      <c r="B179" s="2" t="n"/>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Total existing units</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr"/>
+      <c r="E179" s="2" t="inlineStr"/>
+      <c r="F179" s="2" t="inlineStr"/>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>The total number of existing units</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n"/>
+      <c r="B180" s="2" t="n"/>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Total proposed units</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr"/>
+      <c r="E180" s="2" t="inlineStr"/>
+      <c r="F180" s="2" t="inlineStr"/>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>The total number of proposed units</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n"/>
+      <c r="B181" s="2" t="n"/>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>Net change</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr"/>
+      <c r="E181" s="2" t="inlineStr"/>
+      <c r="F181" s="2" t="inlineStr"/>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>Calculated net change in units</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Site area</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>How big the site is including relevant measurements</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Site area in hectares</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr"/>
+      <c r="E182" s="2" t="inlineStr"/>
+      <c r="F182" s="2" t="inlineStr"/>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>The size of the site in hectares</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n"/>
+      <c r="B183" s="2" t="n"/>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>Site area provided by</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr"/>
+      <c r="E183" s="2" t="inlineStr"/>
+      <c r="F183" s="2" t="inlineStr"/>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>Who provided the site area value</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Site boundary</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr"/>
+      <c r="F184" s="2" t="inlineStr"/>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>wkt</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n"/>
+      <c r="B185" s="2" t="n"/>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr"/>
+      <c r="F185" s="2" t="inlineStr"/>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>Flexible field for capturing addresses</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n"/>
+      <c r="B186" s="2" t="n"/>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr"/>
+      <c r="F186" s="2" t="inlineStr"/>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>The postal code</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n"/>
+      <c r="B187" s="2" t="n"/>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>Easting</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr"/>
+      <c r="F187" s="2" t="inlineStr"/>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n"/>
+      <c r="B188" s="2" t="n"/>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>Northing</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr"/>
+      <c r="F188" s="2" t="inlineStr"/>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n"/>
+      <c r="B189" s="2" t="n"/>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr"/>
+      <c r="F189" s="2" t="inlineStr"/>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n"/>
+      <c r="B190" s="2" t="n"/>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr"/>
+      <c r="F190" s="2" t="inlineStr"/>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n"/>
+      <c r="B191" s="2" t="n"/>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr"/>
+      <c r="F191" s="2" t="inlineStr"/>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>A text description providing details about the subject.</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n"/>
+      <c r="B192" s="2" t="n"/>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr"/>
+      <c r="F192" s="2" t="inlineStr"/>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr"/>
+      <c r="E193" s="2" t="inlineStr"/>
+      <c r="F193" s="2" t="inlineStr"/>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n"/>
+      <c r="B194" s="2" t="n"/>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>Site visit contact type</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr"/>
+      <c r="E194" s="2" t="inlineStr"/>
+      <c r="F194" s="2" t="inlineStr"/>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n"/>
+      <c r="B195" s="2" t="n"/>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr"/>
+      <c r="E195" s="2" t="inlineStr"/>
+      <c r="F195" s="2" t="inlineStr"/>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n"/>
+      <c r="B196" s="2" t="n"/>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr"/>
+      <c r="F196" s="2" t="inlineStr"/>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>The complete name of a person</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n"/>
+      <c r="B197" s="2" t="n"/>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr"/>
+      <c r="F197" s="2" t="inlineStr"/>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n"/>
+      <c r="B198" s="2" t="n"/>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr"/>
+      <c r="F198" s="2" t="inlineStr"/>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Trade effluent</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>Disposal required</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr"/>
+      <c r="E199" s="2" t="inlineStr"/>
+      <c r="F199" s="2" t="inlineStr"/>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n"/>
+      <c r="B200" s="2" t="n"/>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr"/>
+      <c r="E200" s="2" t="inlineStr"/>
+      <c r="F200" s="2" t="inlineStr"/>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Trees and hedges information</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>Trees on site</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr"/>
+      <c r="E201" s="2" t="inlineStr"/>
+      <c r="F201" s="2" t="inlineStr"/>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>Whether trees or hedges are present on the proposed development site</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n"/>
+      <c r="B202" s="2" t="n"/>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>Trees on adjacent land</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr"/>
+      <c r="E202" s="2" t="inlineStr"/>
+      <c r="F202" s="2" t="inlineStr"/>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Vehicle parking</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>Parking spaces[]</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>Parking space type</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr"/>
+      <c r="F203" s="2" t="inlineStr"/>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>Type of parking space or vehicle type</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n"/>
+      <c r="B204" s="2" t="n"/>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>Parking spaces[]</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Vehicle type other</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr"/>
+      <c r="F204" s="2" t="inlineStr"/>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>Vehicle type when parking space type is 'other'</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n"/>
+      <c r="B205" s="2" t="n"/>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>Parking spaces[]</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>Total existing</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr"/>
+      <c r="F205" s="2" t="inlineStr"/>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>Total number of existing parking spaces</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n"/>
+      <c r="B206" s="2" t="n"/>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>Parking spaces[]</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Total proposed</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr"/>
+      <c r="F206" s="2" t="inlineStr"/>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>Total number of proposed parking spaces</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n"/>
+      <c r="B207" s="2" t="n"/>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>Parking spaces[]</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Difference in spaces</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr"/>
+      <c r="F207" s="2" t="inlineStr"/>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>Net change in parking spaces (proposed minus existing)</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Waste storage and collection</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>Needs waste storage area</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr"/>
+      <c r="E208" s="2" t="inlineStr"/>
+      <c r="F208" s="2" t="inlineStr"/>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>Does the proposal require a waste storage area</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n"/>
+      <c r="B209" s="2" t="n"/>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>Waste storage area details</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr"/>
+      <c r="E209" s="2" t="inlineStr"/>
+      <c r="F209" s="2" t="inlineStr"/>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>Details of the waste storage area including location, size, design and access arrangements</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n"/>
+      <c r="B210" s="2" t="n"/>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>Separate recycling arrangements</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr"/>
+      <c r="E210" s="2" t="inlineStr"/>
+      <c r="F210" s="2" t="inlineStr"/>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>Does the proposal include separate recycling arrangements</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n"/>
+      <c r="B211" s="2" t="n"/>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>Separate recycling arrangements details</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr"/>
+      <c r="E211" s="2" t="inlineStr"/>
+      <c r="F211" s="2" t="inlineStr"/>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
           <t>Details of the recycling arrangements including types of materials, collection methods and storage facilities</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I149" s="2" t="inlineStr">
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
@@ -5155,68 +7189,68 @@
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="B49"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="B75:B78"/>
-    <mergeCell ref="A106"/>
-    <mergeCell ref="B26:B33"/>
-    <mergeCell ref="B134:B139"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="B89"/>
-    <mergeCell ref="B142"/>
-    <mergeCell ref="A59:A68"/>
-    <mergeCell ref="B80"/>
-    <mergeCell ref="B59:B68"/>
-    <mergeCell ref="A95:A105"/>
-    <mergeCell ref="B79"/>
-    <mergeCell ref="B2:B18"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="A81:A87"/>
+    <mergeCell ref="B65"/>
+    <mergeCell ref="A94:A97"/>
+    <mergeCell ref="B193:B198"/>
+    <mergeCell ref="B94:B97"/>
+    <mergeCell ref="B199:B200"/>
+    <mergeCell ref="B148:B158"/>
+    <mergeCell ref="A2:A19"/>
+    <mergeCell ref="B72:B77"/>
+    <mergeCell ref="A203:A207"/>
+    <mergeCell ref="B208:B211"/>
+    <mergeCell ref="B182:B183"/>
+    <mergeCell ref="A208:A211"/>
+    <mergeCell ref="A30:A37"/>
+    <mergeCell ref="A128:A142"/>
+    <mergeCell ref="B98:B101"/>
+    <mergeCell ref="A88:A93"/>
     <mergeCell ref="B143:B147"/>
-    <mergeCell ref="A75:A78"/>
-    <mergeCell ref="A48"/>
-    <mergeCell ref="A123:A124"/>
-    <mergeCell ref="A69:A74"/>
-    <mergeCell ref="B106"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="B47"/>
+    <mergeCell ref="B51:B64"/>
+    <mergeCell ref="A184:A192"/>
+    <mergeCell ref="A109:A115"/>
+    <mergeCell ref="B66:B68"/>
     <mergeCell ref="A143:A147"/>
-    <mergeCell ref="A49"/>
-    <mergeCell ref="B38:B43"/>
-    <mergeCell ref="A125:A133"/>
-    <mergeCell ref="A142"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="A79"/>
-    <mergeCell ref="A88"/>
-    <mergeCell ref="B48"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="B69:B74"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="A107:A122"/>
-    <mergeCell ref="A2:A18"/>
-    <mergeCell ref="B95:B105"/>
-    <mergeCell ref="B90:B94"/>
-    <mergeCell ref="B81:B87"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="B53:B58"/>
-    <mergeCell ref="B123:B124"/>
-    <mergeCell ref="A80"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="B125:B133"/>
-    <mergeCell ref="A134:A139"/>
-    <mergeCell ref="A89"/>
-    <mergeCell ref="A26:A33"/>
-    <mergeCell ref="B88"/>
-    <mergeCell ref="A53:A58"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="A38:A43"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="B107:B122"/>
-    <mergeCell ref="A90:A94"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="A47"/>
+    <mergeCell ref="B166:B181"/>
+    <mergeCell ref="B42:B47"/>
+    <mergeCell ref="A159:A165"/>
+    <mergeCell ref="A193:A198"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="A102:A108"/>
+    <mergeCell ref="A78:A87"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="B88:B93"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A51:A64"/>
+    <mergeCell ref="B201:B202"/>
+    <mergeCell ref="A65"/>
+    <mergeCell ref="B109:B115"/>
+    <mergeCell ref="A69:A71"/>
+    <mergeCell ref="B203:B207"/>
+    <mergeCell ref="B128:B142"/>
+    <mergeCell ref="B159:B165"/>
+    <mergeCell ref="A199:A200"/>
+    <mergeCell ref="B116:B127"/>
+    <mergeCell ref="A166:A181"/>
+    <mergeCell ref="A66:A68"/>
+    <mergeCell ref="A42:A47"/>
+    <mergeCell ref="B78:B87"/>
+    <mergeCell ref="B184:B192"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A148:A158"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="B30:B37"/>
+    <mergeCell ref="A20:A25"/>
+    <mergeCell ref="A201:A202"/>
+    <mergeCell ref="B20:B25"/>
+    <mergeCell ref="A72:A77"/>
+    <mergeCell ref="B2:B19"/>
+    <mergeCell ref="B69:B71"/>
+    <mergeCell ref="B102:B108"/>
+    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="A116:A127"/>
+    <mergeCell ref="A98:A101"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/technical-details-consent-technical-details-consent.xlsx
+++ b/generated/spreadsheet/technical-details-consent-technical-details-consent.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I211"/>
+  <dimension ref="A1:I214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -1587,13 +1587,17 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>Address Text</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1622,13 +1626,17 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1652,14 +1660,22 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1683,19 +1699,19 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -1705,58 +1721,58 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n"/>
-      <c r="B39" s="2" t="n"/>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1780,18 +1796,14 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1801,7 +1813,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1820,18 +1832,18 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -1841,47 +1853,51 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n"/>
-      <c r="B43" s="2" t="n"/>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1889,18 +1905,14 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -1910,7 +1922,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1929,13 +1941,13 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -1945,7 +1957,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1964,13 +1976,13 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -1999,13 +2011,13 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2034,58 +2046,66 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Text representation of an address or site</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>The postal code</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Postcode for a contact address or site</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity, geological and archaeological conservation</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Protected species impact</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr"/>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Where is there a likelihood of protected and priority species being affected?</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2094,34 +2114,54 @@
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity features impact</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr"/>
-      <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="2" t="n"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity, geological and archaeological conservation</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
+        </is>
+      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Geological features impact</t>
+          <t>Protected species impact</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -2129,7 +2169,7 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
+          <t>Where is there a likelihood of protected and priority species being affected?</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2144,19 +2184,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity net gain</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition applies</t>
+          <t>Biodiversity features impact</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -2164,12 +2196,12 @@
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
+          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2183,19 +2215,15 @@
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition exemption reason[]</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Exemption type</t>
-        </is>
-      </c>
+          <t>Geological features impact</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
+          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2210,28 +2238,32 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n"/>
-      <c r="B53" s="2" t="n"/>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity net gain</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
+        </is>
+      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition exemption reason[]</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
+          <t>Biodiversity gain condition applies</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>The reason the exemption applies to this proposal</t>
+          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2245,24 +2277,24 @@
       <c r="B54" s="2" t="n"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain details</t>
+          <t>Biodiversity gain condition exemption reason[]</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Pre development date</t>
+          <t>Exemption type</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
+          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2276,24 +2308,24 @@
       <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain details</t>
+          <t>Biodiversity gain condition exemption reason[]</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Pre development biodiversity value</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
+          <t>The reason the exemption applies to this proposal</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2312,24 +2344,24 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Earlier date reason</t>
+          <t>Pre development date</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Reason for using a pre-development date that is earlier than the application submission</t>
+          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2343,24 +2375,24 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss after 2020</t>
+          <t>Pre development biodiversity value</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
+          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2374,28 +2406,24 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss details</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>Loss date</t>
-        </is>
-      </c>
+          <t>Earlier date reason</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Date the activity causing habitat loss or degradation occurred</t>
+          <t>Reason for using a pre-development date that is earlier than the application submission</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2409,28 +2437,24 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss details</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>Pre loss biodiversity value</t>
-        </is>
-      </c>
+          <t>Habitat loss after 2020</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
+          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2449,23 +2473,23 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Supporting evidence</t>
+          <t>Loss date</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
+          <t>Date the activity causing habitat loss or degradation occurred</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2479,19 +2503,23 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Metric publication date</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Pre loss biodiversity value</t>
+        </is>
+      </c>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Publication date of the biodiversity metric tool used for calculations</t>
+          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -2510,24 +2538,28 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Supporting evidence</t>
+        </is>
+      </c>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether the site contains any irreplaceable habitats</t>
+          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2541,24 +2573,24 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats details</t>
+          <t>Metric publication date</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Description and references for any irreplaceable habitats identified on the site</t>
+          <t>Publication date of the biodiversity metric tool used for calculations</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2572,23 +2604,19 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Irreplaceable habitats</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Indicates whether the site contains any irreplaceable habitats</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -2598,27 +2626,23 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr"/>
+          <t>Biodiversity net gain details</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Irreplaceable habitats details</t>
+        </is>
+      </c>
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Description and references for any irreplaceable habitats identified on the site</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -2628,37 +2652,37 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr"/>
-      <c r="E66" s="2" t="inlineStr"/>
+          <t>Biodiversity net gain details</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -2668,11 +2692,19 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n"/>
-      <c r="B67" s="2" t="n"/>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+        </is>
+      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
@@ -2680,7 +2712,7 @@
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Reference to the applicant or agent with the conflict</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -2690,16 +2722,24 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n"/>
-      <c r="B68" s="2" t="n"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
@@ -2707,31 +2747,23 @@
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Person reference</t>
@@ -2742,7 +2774,7 @@
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -2752,7 +2784,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2793,7 @@
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
@@ -2769,26 +2801,34 @@
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n"/>
-      <c r="B71" s="2" t="n"/>
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
@@ -2796,12 +2836,12 @@
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -2811,36 +2851,24 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>How the proposed development will impact existing and proposed employee numbers</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="n"/>
+      <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
+          <t>Declaration confirmed</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr"/>
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -2854,24 +2882,20 @@
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>Part-time</t>
-        </is>
-      </c>
+          <t>Declaration date</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr"/>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -2881,8 +2905,16 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n"/>
-      <c r="B74" s="2" t="n"/>
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>How the proposed development will impact existing and proposed employee numbers</t>
+        </is>
+      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>Existing employees</t>
@@ -2890,19 +2922,19 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -2916,19 +2948,19 @@
       <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Existing employees</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -2947,24 +2979,24 @@
       <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Existing employees</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -2983,19 +3015,19 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -3005,36 +3037,28 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Existing use</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>How the site is currently being used.</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
+          <t>Proposed employees</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -3048,35 +3072,43 @@
       <c r="B79" s="2" t="n"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
+          <t>Proposed employees</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Use details</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Further detail of the use</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n"/>
-      <c r="B80" s="2" t="n"/>
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Existing use</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>How the site is currently being used.</t>
+        </is>
+      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>Existing use details[]</t>
@@ -3084,19 +3116,19 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Land part</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Which part of the land the use relates to</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -3110,25 +3142,29 @@
       <c r="B81" s="2" t="n"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Site vacant</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr"/>
+          <t>Existing use details[]</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Use details</t>
+        </is>
+      </c>
       <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Is the site currently vacant</t>
+          <t>Further detail of the use</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3137,15 +3173,19 @@
       <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Last use details</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr"/>
+          <t>Existing use details[]</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Land part</t>
+        </is>
+      </c>
       <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Description of the last use of the site</t>
+          <t>Which part of the land the use relates to</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -3155,7 +3195,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3204,7 @@
       <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Last use end date</t>
+          <t>Site vacant</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
@@ -3172,17 +3212,17 @@
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Date the last use ended (YYYY-MM-DD format)</t>
+          <t>Is the site currently vacant</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3231,7 @@
       <c r="B84" s="2" t="n"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Is contaminated land</t>
+          <t>Last use details</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
@@ -3199,17 +3239,17 @@
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Is the site known to be contaminated?</t>
+          <t>Description of the last use of the site</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3258,7 @@
       <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Is suspected contaminated land</t>
+          <t>Last use end date</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
@@ -3226,17 +3266,17 @@
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Is the site suspected of contamination?</t>
+          <t>Date the last use ended (YYYY-MM-DD format)</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3245,7 +3285,7 @@
       <c r="B86" s="2" t="n"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Proposed use contamination risk</t>
+          <t>Is contaminated land</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
@@ -3253,7 +3293,7 @@
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Is the proposed use vulnerable to the presence of contamination?</t>
+          <t>Is the site known to be contaminated?</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -3272,7 +3312,7 @@
       <c r="B87" s="2" t="n"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Contamination assessment</t>
+          <t>Is suspected contaminated land</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
@@ -3280,34 +3320,26 @@
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Reference to contamination assessment document</t>
+          <t>Is the site suspected of contamination?</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Flood risk assessment</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>Results of any flood risk assessments made for the development site</t>
-        </is>
-      </c>
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="n"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Flood risk area</t>
+          <t>Proposed use contamination risk</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
@@ -3315,7 +3347,7 @@
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Is the site within an area at risk of flooding?</t>
+          <t>Is the proposed use vulnerable to the presence of contamination?</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -3334,7 +3366,7 @@
       <c r="B89" s="2" t="n"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Data provided by</t>
+          <t>Contamination assessment</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
@@ -3342,12 +3374,12 @@
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Who provided the data: Applicant or System/Service?</t>
+          <t>Reference to contamination assessment document</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -3357,11 +3389,19 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n"/>
-      <c r="B90" s="2" t="n"/>
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Flood risk assessment</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Results of any flood risk assessments made for the development site</t>
+        </is>
+      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Flood risk assessment</t>
+          <t>Flood risk area</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
@@ -3369,17 +3409,17 @@
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Reference of the flood risk assessment document</t>
+          <t>Is the site within an area at risk of flooding?</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3428,7 @@
       <c r="B91" s="2" t="n"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Within 20m watercourse</t>
+          <t>Data provided by</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
@@ -3396,17 +3436,17 @@
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Whether the development is within 20 metres of a watercourse</t>
+          <t>Who provided the data: Applicant or System/Service?</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3455,7 @@
       <c r="B92" s="2" t="n"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Increases flood risk</t>
+          <t>Flood risk assessment</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr"/>
@@ -3423,17 +3463,17 @@
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Whether the development increases flood risk</t>
+          <t>Reference of the flood risk assessment document</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3482,7 @@
       <c r="B93" s="2" t="n"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Surface water disposal[]</t>
+          <t>Within 20m watercourse</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
@@ -3450,12 +3490,12 @@
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Method for disposing of surface water</t>
+          <t>Whether the development is within 20 metres of a watercourse</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -3465,19 +3505,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>Foul sewage disposal</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>How waste water will leave the property as part of the proposed development</t>
-        </is>
-      </c>
+      <c r="A94" s="2" t="n"/>
+      <c r="B94" s="2" t="n"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Has new disposal arrangements</t>
+          <t>Increases flood risk</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
@@ -3485,7 +3517,7 @@
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include any new foul sewage disposal arrangments</t>
+          <t>Whether the development increases flood risk</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -3504,7 +3536,7 @@
       <c r="B95" s="2" t="n"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Foul sewage disposal types[]</t>
+          <t>Surface water disposal[]</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
@@ -3512,7 +3544,7 @@
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>List of ways foul sewage will be disposed of</t>
+          <t>Method for disposing of surface water</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -3522,16 +3554,24 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n"/>
-      <c r="B96" s="2" t="n"/>
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Foul sewage disposal</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>How waste water will leave the property as part of the proposed development</t>
+        </is>
+      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Connect to drainage system</t>
+          <t>Has new disposal arrangements</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
@@ -3539,7 +3579,7 @@
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal needs to connect to the existing drainage system</t>
+          <t>Does the proposal include any new foul sewage disposal arrangments</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -3558,46 +3598,34 @@
       <c r="B97" s="2" t="n"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Foul sewage disposal types[]</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr"/>
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>List of ways foul sewage will be disposed of</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous substances</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>Details of hazardous substances requiring consent used as part of the development</t>
-        </is>
-      </c>
+      <c r="A98" s="2" t="n"/>
+      <c r="B98" s="2" t="n"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Involves hazardous substances</t>
+          <t>Connect to drainage system</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr"/>
@@ -3605,12 +3633,12 @@
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Indicates if hazardous substances are involved in the proposal</t>
+          <t>Whether the proposal needs to connect to the existing drainage system</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -3624,24 +3652,24 @@
       <c r="B99" s="2" t="n"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Substance types[]</t>
+          <t>Supporting documents[]</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Hazardous substance type</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Reference of hazardous substance type from predefined list</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -3651,33 +3679,37 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n"/>
-      <c r="B100" s="2" t="n"/>
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Hazardous substances</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Details of hazardous substances requiring consent used as part of the development</t>
+        </is>
+      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Substance types[]</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous substance other</t>
-        </is>
-      </c>
+          <t>Involves hazardous substances</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr"/>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>The specific name of the hazardous substance if other is selected</t>
+          <t>Indicates if hazardous substances are involved in the proposal</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3691,19 +3723,19 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Hazardous substance type</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>Reference of hazardous substance type from predefined list</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -3713,41 +3745,33 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>Hours of operation</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
-        </is>
-      </c>
+      <c r="A102" s="2" t="n"/>
+      <c r="B102" s="2" t="n"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation[]</t>
+          <t>Substance types[]</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Hazardous substance other</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>The specific name of the hazardous substance if other is selected</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3756,35 +3780,43 @@
       <c r="B103" s="2" t="n"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation[]</t>
+          <t>Substance types[]</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Use other</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n"/>
-      <c r="B104" s="2" t="n"/>
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Hours of operation</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
+        </is>
+      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>Hours of operation[]</t>
@@ -3792,18 +3824,14 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Operational times[]</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>Schedule days[]</t>
-        </is>
-      </c>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>List of days or day categories that a schedule entry applies to</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -3827,23 +3855,19 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Operational times[]</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
+          <t>Use other</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>True or False - explicitly state when closed</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -3867,22 +3891,18 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Time ranges[]</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>Open time</t>
-        </is>
-      </c>
+          <t>Schedule days[]</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Opening time</t>
+          <t>List of days or day categories that a schedule entry applies to</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
@@ -3906,27 +3926,23 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Time ranges[]</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>Close time</t>
-        </is>
-      </c>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Closing time</t>
+          <t>True or False - explicitly state when closed</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3940,54 +3956,66 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Hours not known</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr"/>
-      <c r="F108" s="2" t="inlineStr"/>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Open time</t>
+        </is>
+      </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Applicant states they do not know the hours of operation</t>
+          <t>Opening time</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>What materials are being used for the proposed development</t>
-        </is>
-      </c>
+      <c r="A109" s="2" t="n"/>
+      <c r="B109" s="2" t="n"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Proposal material details</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr"/>
-      <c r="E109" s="2" t="inlineStr"/>
-      <c r="F109" s="2" t="inlineStr"/>
+          <t>Hours of operation[]</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Close time</t>
+        </is>
+      </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves material details that need to be provided</t>
+          <t>Closing time</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -4001,60 +4029,64 @@
       <c r="B110" s="2" t="n"/>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
+          <t>Hours of operation[]</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Building element type</t>
+          <t>Hours not known</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Applicant states they do not know the hours of operation</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n"/>
-      <c r="B111" s="2" t="n"/>
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>What materials are being used for the proposed development</t>
+        </is>
+      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>Existing materials</t>
-        </is>
-      </c>
+          <t>Proposal material details</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr"/>
       <c r="E111" s="2" t="inlineStr"/>
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>Whether the proposal involves material details that need to be provided</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4068,24 +4100,24 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Building element type</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4099,19 +4131,19 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Materials not known</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr"/>
       <c r="F113" s="2" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Indicates the materials for this building element are not yet known</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
@@ -4125,25 +4157,29 @@
       <c r="B114" s="2" t="n"/>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Providing additional material information</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr"/>
+          <t>Building elements[]</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Proposed materials</t>
+        </is>
+      </c>
       <c r="E114" s="2" t="inlineStr"/>
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4152,46 +4188,38 @@
       <c r="B115" s="2" t="n"/>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
+          <t>Building elements[]</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Materials not known</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr"/>
       <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Indicates the materials for this building element are not yet known</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>Non residential floorspace</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>Details of changes to non-residential floorspace in the proposed development.</t>
-        </is>
-      </c>
+      <c r="A116" s="2" t="n"/>
+      <c r="B116" s="2" t="n"/>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Non residential change</t>
+          <t>Providing additional material information</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr"/>
@@ -4199,7 +4227,7 @@
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
+          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -4218,24 +4246,24 @@
       <c r="B117" s="2" t="n"/>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Floorspace details[]</t>
+          <t>Supporting documents[]</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr"/>
       <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
@@ -4245,33 +4273,37 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n"/>
-      <c r="B118" s="2" t="n"/>
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Non residential floorspace</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Details of changes to non-residential floorspace in the proposed development.</t>
+        </is>
+      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Floorspace details[]</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>Specified use</t>
-        </is>
-      </c>
+          <t>Non residential change</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr"/>
       <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>A specified use if no applicable use class is available</t>
+          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4285,19 +4317,19 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Existing gross floorspace</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Existing gross internal floorspace, in sqm</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
@@ -4316,24 +4348,24 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Floorspace lost</t>
+          <t>Specified use</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Gross floorspace to be lost by change of use, in sqm</t>
+          <t>A specified use if no applicable use class is available</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4347,14 +4379,14 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Total gross proposed</t>
+          <t>Existing gross floorspace</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
       <c r="F121" s="2" t="inlineStr"/>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Total gross internal floorspace proposed, in sqm</t>
+          <t>Existing gross internal floorspace, in sqm</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -4378,14 +4410,14 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Net additional floorspace</t>
+          <t>Floorspace lost</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Net additional gross internal floorspace, in sqm</t>
+          <t>Gross floorspace to be lost by change of use, in sqm</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -4404,24 +4436,24 @@
       <c r="B123" s="2" t="n"/>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Room details[]</t>
+          <t>Floorspace details[]</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Use class for accommodation</t>
+          <t>Total gross proposed</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr"/>
       <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Type of non-residential use class referring to accommodation uses</t>
+          <t>Total gross internal floorspace proposed, in sqm</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
@@ -4435,29 +4467,29 @@
       <c r="B124" s="2" t="n"/>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Room details[]</t>
+          <t>Floorspace details[]</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Use other</t>
+          <t>Net additional floorspace</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>Net additional gross internal floorspace, in sqm</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4471,19 +4503,19 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Existing rooms lost</t>
+          <t>Use class for accommodation</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
       <c r="F125" s="2" t="inlineStr"/>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Existing rooms to be lost by change of use</t>
+          <t>Type of non-residential use class referring to accommodation uses</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
@@ -4502,24 +4534,24 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Total rooms proposed</t>
+          <t>Use other</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Total rooms proposed (including change of use)</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4533,14 +4565,14 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Net additional rooms</t>
+          <t>Existing rooms lost</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr"/>
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Net additional rooms following development</t>
+          <t>Existing rooms to be lost by change of use</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -4555,32 +4587,28 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
-        </is>
-      </c>
+      <c r="A128" s="2" t="n"/>
+      <c r="B128" s="2" t="n"/>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr"/>
+          <t>Room details[]</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Total rooms proposed</t>
+        </is>
+      </c>
       <c r="E128" s="2" t="inlineStr"/>
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Total rooms proposed (including change of use)</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
@@ -4594,20 +4622,24 @@
       <c r="B129" s="2" t="n"/>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr"/>
+          <t>Room details[]</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Net additional rooms</t>
+        </is>
+      </c>
       <c r="E129" s="2" t="inlineStr"/>
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>Net additional rooms following development</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
@@ -4617,37 +4649,37 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n"/>
-      <c r="B130" s="2" t="n"/>
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+        </is>
+      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr"/>
+      <c r="E130" s="2" t="inlineStr"/>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4656,28 +4688,20 @@
       <c r="B131" s="2" t="n"/>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
+          <t>Agricultural tenants</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr"/>
+      <c r="E131" s="2" t="inlineStr"/>
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
@@ -4701,13 +4725,13 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -4717,7 +4741,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4736,13 +4760,13 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -4771,13 +4795,13 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -4787,7 +4811,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4801,24 +4825,32 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Notice served date</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr"/>
-      <c r="F135" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4827,20 +4859,32 @@
       <c r="B136" s="2" t="n"/>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr"/>
-      <c r="E136" s="2" t="inlineStr"/>
-      <c r="F136" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
@@ -4854,15 +4898,27 @@
       <c r="B137" s="2" t="n"/>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr"/>
-      <c r="E137" s="2" t="inlineStr"/>
-      <c r="F137" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -4881,29 +4937,29 @@
       <c r="B138" s="2" t="n"/>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
+          <t>Owners and tenants[]</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Notice served date</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4912,29 +4968,25 @@
       <c r="B139" s="2" t="n"/>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr"/>
       <c r="E139" s="2" t="inlineStr"/>
       <c r="F139" s="2" t="inlineStr"/>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4995,7 @@
       <c r="B140" s="2" t="n"/>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Steps taken</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr"/>
@@ -4951,7 +5003,7 @@
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -4961,7 +5013,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4970,20 +5022,24 @@
       <c r="B141" s="2" t="n"/>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="E141" s="2" t="inlineStr"/>
       <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
@@ -4997,15 +5053,19 @@
       <c r="B142" s="2" t="n"/>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="E142" s="2" t="inlineStr"/>
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -5020,19 +5080,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A143" s="2" t="n"/>
+      <c r="B143" s="2" t="n"/>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr"/>
@@ -5040,12 +5092,12 @@
       <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
@@ -5059,7 +5111,7 @@
       <c r="B144" s="2" t="n"/>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr"/>
@@ -5067,17 +5119,17 @@
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5138,7 @@
       <c r="B145" s="2" t="n"/>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr"/>
@@ -5094,26 +5146,34 @@
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n"/>
-      <c r="B146" s="2" t="n"/>
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr"/>
@@ -5121,17 +5181,17 @@
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5200,7 @@
       <c r="B147" s="2" t="n"/>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr"/>
@@ -5148,7 +5208,7 @@
       <c r="F147" s="2" t="inlineStr"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -5163,20 +5223,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>Processes machinery waste</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">How waste will be managed on the site
-</t>
-        </is>
-      </c>
+      <c r="A148" s="2" t="n"/>
+      <c r="B148" s="2" t="n"/>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Site activity details</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr"/>
@@ -5184,7 +5235,7 @@
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -5194,7 +5245,7 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5254,7 @@
       <c r="B149" s="2" t="n"/>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Proposal waste management</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr"/>
@@ -5211,17 +5262,17 @@
       <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves any waste management facility that is relevant to the proposal</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5230,55 +5281,56 @@
       <c r="B150" s="2" t="n"/>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>Waste management facility type</t>
-        </is>
-      </c>
+          <t>Advice summary</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr"/>
       <c r="E150" s="2" t="inlineStr"/>
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Type of waste management facility being described in this entry</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n"/>
-      <c r="B151" s="2" t="n"/>
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Processes machinery waste</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
+        </is>
+      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
-        <is>
-          <t>Total capacity</t>
-        </is>
-      </c>
+          <t>Site activity details</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr"/>
       <c r="E151" s="2" t="inlineStr"/>
       <c r="F151" s="2" t="inlineStr"/>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
+          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
@@ -5292,24 +5344,20 @@
       <c r="B152" s="2" t="n"/>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>Unit type</t>
-        </is>
-      </c>
+          <t>Proposal waste management</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr"/>
       <c r="E152" s="2" t="inlineStr"/>
       <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Whether the proposal involves any waste management facility that is relevant to the proposal</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
@@ -5328,19 +5376,19 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Annual throughput</t>
+          <t>Waste management facility type</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr"/>
       <c r="F153" s="2" t="inlineStr"/>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Maximum annual operational throughput in tonnes/litres</t>
+          <t>Type of waste management facility being described in this entry</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
@@ -5359,19 +5407,19 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Total capacity</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
@@ -5385,29 +5433,29 @@
       <c r="B155" s="2" t="n"/>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
+          <t>Waste management[]</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr"/>
       <c r="F155" s="2" t="inlineStr"/>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5416,19 +5464,19 @@
       <c r="B156" s="2" t="n"/>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
+          <t>Waste management[]</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Construction demolition</t>
+          <t>Annual throughput</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr"/>
       <c r="F156" s="2" t="inlineStr"/>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum annual operational throughput in tonnes/litres</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -5438,7 +5486,7 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5447,29 +5495,29 @@
       <c r="B157" s="2" t="n"/>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
+          <t>Waste management[]</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Commercial industrial</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr"/>
       <c r="F157" s="2" t="inlineStr"/>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5483,14 +5531,14 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Hazardous</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr"/>
       <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -5505,37 +5553,33 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>What development, works or change of use is proposed</t>
-        </is>
-      </c>
+      <c r="A159" s="2" t="n"/>
+      <c r="B159" s="2" t="n"/>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr"/>
+          <t>Waste streams throughput</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Construction demolition</t>
+        </is>
+      </c>
       <c r="E159" s="2" t="inlineStr"/>
       <c r="F159" s="2" t="inlineStr"/>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5544,25 +5588,29 @@
       <c r="B160" s="2" t="n"/>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr"/>
+          <t>Waste streams throughput</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Commercial industrial</t>
+        </is>
+      </c>
       <c r="E160" s="2" t="inlineStr"/>
       <c r="F160" s="2" t="inlineStr"/>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5571,20 +5619,24 @@
       <c r="B161" s="2" t="n"/>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr"/>
+          <t>Waste streams throughput</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Hazardous</t>
+        </is>
+      </c>
       <c r="E161" s="2" t="inlineStr"/>
       <c r="F161" s="2" t="inlineStr"/>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
@@ -5594,11 +5646,19 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n"/>
-      <c r="B162" s="2" t="n"/>
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>What development, works or change of use is proposed</t>
+        </is>
+      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr"/>
@@ -5606,12 +5666,12 @@
       <c r="F162" s="2" t="inlineStr"/>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
@@ -5625,7 +5685,7 @@
       <c r="B163" s="2" t="n"/>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr"/>
@@ -5633,17 +5693,17 @@
       <c r="F163" s="2" t="inlineStr"/>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5712,7 @@
       <c r="B164" s="2" t="n"/>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>PIP reference</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr"/>
@@ -5660,12 +5720,12 @@
       <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Reference number for the Planning in Principle (PIP) application this relates to</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
@@ -5679,7 +5739,7 @@
       <c r="B165" s="2" t="n"/>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Is public service infrastructure</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr"/>
@@ -5687,7 +5747,7 @@
       <c r="F165" s="2" t="inlineStr"/>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>For applications made on or after 1 August 2021, is the proposal for public service infrastructure development</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -5702,19 +5762,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>Residential units</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>Details of the residential units that make up both the current and proposed development.</t>
-        </is>
-      </c>
+      <c r="A166" s="2" t="n"/>
+      <c r="B166" s="2" t="n"/>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Residential unit change</t>
+          <t>Proposal completion date</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr"/>
@@ -5722,17 +5774,17 @@
       <c r="F166" s="2" t="inlineStr"/>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Proposal includes the gain, loss or change of use of residential units</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5741,29 +5793,25 @@
       <c r="B167" s="2" t="n"/>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
-        <is>
-          <t>Tenure type</t>
-        </is>
-      </c>
+          <t>PIP reference</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr"/>
       <c r="E167" s="2" t="inlineStr"/>
       <c r="F167" s="2" t="inlineStr"/>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Category of housing tenure</t>
+          <t>Reference number for the Planning in Principle (PIP) application this relates to</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5772,24 +5820,20 @@
       <c r="B168" s="2" t="n"/>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
-        <is>
-          <t>Housing type</t>
-        </is>
-      </c>
+          <t>Is public service infrastructure</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr"/>
       <c r="E168" s="2" t="inlineStr"/>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Type of housing</t>
+          <t>For applications made on or after 1 August 2021, is the proposal for public service infrastructure development</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
@@ -5799,27 +5843,27 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n"/>
-      <c r="B169" s="2" t="n"/>
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Residential units</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Details of the residential units that make up both the current and proposed development.</t>
+        </is>
+      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Existing unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
-        <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
+          <t>Residential unit change</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr"/>
+      <c r="E169" s="2" t="inlineStr"/>
       <c r="F169" s="2" t="inlineStr"/>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Proposal includes the gain, loss or change of use of residential units</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -5843,27 +5887,19 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Existing unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="E170" s="2" t="inlineStr">
-        <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F170" s="2" t="inlineStr">
-        <is>
-          <t>No bedrooms unknown</t>
-        </is>
-      </c>
+          <t>Tenure type</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr"/>
+      <c r="F170" s="2" t="inlineStr"/>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>Category of housing tenure</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
@@ -5882,32 +5918,24 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Existing unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
-        <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>Number of bedrooms</t>
-        </is>
-      </c>
+          <t>Housing type</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr"/>
+      <c r="F171" s="2" t="inlineStr"/>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>Type of housing</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5926,22 +5954,18 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F172" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Units unknown</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr"/>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
@@ -5965,23 +5989,27 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>Total units</t>
-        </is>
-      </c>
-      <c r="F173" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5995,28 +6023,32 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Proposed unit breakdown[]</t>
+          <t>Existing unit breakdown[]</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="F174" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Number of bedrooms</t>
+        </is>
+      </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6062,7 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Proposed unit breakdown[]</t>
+          <t>Existing unit breakdown[]</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -6040,17 +6072,17 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
@@ -6069,22 +6101,18 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Proposed unit breakdown[]</t>
+          <t>Existing unit breakdown[]</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F176" s="2" t="inlineStr">
-        <is>
-          <t>Number of bedrooms</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr"/>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -6113,22 +6141,18 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F177" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Units unknown</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr"/>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
@@ -6152,23 +6176,27 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>Total units</t>
-        </is>
-      </c>
-      <c r="F178" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6177,15 +6205,27 @@
       <c r="B179" s="2" t="n"/>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Total existing units</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr"/>
-      <c r="E179" s="2" t="inlineStr"/>
-      <c r="F179" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Proposed unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>Number of bedrooms</t>
+        </is>
+      </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>The total number of existing units</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -6195,7 +6235,7 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6204,15 +6244,27 @@
       <c r="B180" s="2" t="n"/>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Total proposed units</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr"/>
-      <c r="E180" s="2" t="inlineStr"/>
-      <c r="F180" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Proposed unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>The total number of proposed units</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -6231,15 +6283,23 @@
       <c r="B181" s="2" t="n"/>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Net change</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr"/>
-      <c r="E181" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Proposed unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>Total units</t>
+        </is>
+      </c>
       <c r="F181" s="2" t="inlineStr"/>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>Calculated net change in units</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
@@ -6249,24 +6309,16 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="inlineStr">
-        <is>
-          <t>Site area</t>
-        </is>
-      </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>How big the site is including relevant measurements</t>
-        </is>
-      </c>
+      <c r="A182" s="2" t="n"/>
+      <c r="B182" s="2" t="n"/>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Site area in hectares</t>
+          <t>Total existing units</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr"/>
@@ -6274,12 +6326,12 @@
       <c r="F182" s="2" t="inlineStr"/>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>The size of the site in hectares</t>
+          <t>The total number of existing units</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
@@ -6293,7 +6345,7 @@
       <c r="B183" s="2" t="n"/>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Site area provided by</t>
+          <t>Total proposed units</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr"/>
@@ -6301,87 +6353,79 @@
       <c r="F183" s="2" t="inlineStr"/>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>Who provided the site area value</t>
+          <t>The total number of proposed units</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A184" s="2" t="n"/>
+      <c r="B184" s="2" t="n"/>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
-        <is>
-          <t>Site boundary</t>
-        </is>
-      </c>
+          <t>Net change</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr"/>
       <c r="E184" s="2" t="inlineStr"/>
       <c r="F184" s="2" t="inlineStr"/>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Calculated net change in units</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n"/>
-      <c r="B185" s="2" t="n"/>
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>Site area</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>How big the site is including relevant measurements</t>
+        </is>
+      </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>Site area in hectares</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr"/>
       <c r="E185" s="2" t="inlineStr"/>
       <c r="F185" s="2" t="inlineStr"/>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The size of the site in hectares</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6390,24 +6434,20 @@
       <c r="B186" s="2" t="n"/>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Site area provided by</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr"/>
       <c r="E186" s="2" t="inlineStr"/>
       <c r="F186" s="2" t="inlineStr"/>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Who provided the site area value</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
@@ -6417,8 +6457,16 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n"/>
-      <c r="B187" s="2" t="n"/>
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -6426,24 +6474,24 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr"/>
       <c r="F187" s="2" t="inlineStr"/>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6457,24 +6505,28 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
-        </is>
-      </c>
-      <c r="E188" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="F188" s="2" t="inlineStr"/>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6488,19 +6540,23 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="E189" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F189" s="2" t="inlineStr"/>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
@@ -6519,19 +6575,23 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="E190" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="F190" s="2" t="inlineStr"/>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
@@ -6550,14 +6610,18 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="E191" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="F191" s="2" t="inlineStr"/>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject.</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -6581,19 +6645,19 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr"/>
       <c r="F192" s="2" t="inlineStr"/>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
@@ -6603,37 +6667,33 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A193" s="2" t="n"/>
+      <c r="B193" s="2" t="n"/>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Northing</t>
+        </is>
+      </c>
       <c r="E193" s="2" t="inlineStr"/>
       <c r="F193" s="2" t="inlineStr"/>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6642,25 +6702,29 @@
       <c r="B194" s="2" t="n"/>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
       <c r="E194" s="2" t="inlineStr"/>
       <c r="F194" s="2" t="inlineStr"/>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6669,20 +6733,24 @@
       <c r="B195" s="2" t="n"/>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
       <c r="E195" s="2" t="inlineStr"/>
       <c r="F195" s="2" t="inlineStr"/>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
@@ -6692,28 +6760,32 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n"/>
-      <c r="B196" s="2" t="n"/>
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D196" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr"/>
       <c r="E196" s="2" t="inlineStr"/>
       <c r="F196" s="2" t="inlineStr"/>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
@@ -6727,24 +6799,20 @@
       <c r="B197" s="2" t="n"/>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Site visit contact type</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr"/>
       <c r="E197" s="2" t="inlineStr"/>
       <c r="F197" s="2" t="inlineStr"/>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
@@ -6758,19 +6826,15 @@
       <c r="B198" s="2" t="n"/>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr"/>
       <c r="E198" s="2" t="inlineStr"/>
       <c r="F198" s="2" t="inlineStr"/>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -6780,37 +6844,33 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>Trade effluent</t>
-        </is>
-      </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
-        </is>
-      </c>
+      <c r="A199" s="2" t="n"/>
+      <c r="B199" s="2" t="n"/>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Disposal required</t>
-        </is>
-      </c>
-      <c r="D199" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="E199" s="2" t="inlineStr"/>
       <c r="F199" s="2" t="inlineStr"/>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
@@ -6824,15 +6884,19 @@
       <c r="B200" s="2" t="n"/>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D200" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="E200" s="2" t="inlineStr"/>
       <c r="F200" s="2" t="inlineStr"/>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -6842,37 +6906,33 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>Trees and hedges information</t>
-        </is>
-      </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
-        </is>
-      </c>
+      <c r="A201" s="2" t="n"/>
+      <c r="B201" s="2" t="n"/>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Trees on site</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="E201" s="2" t="inlineStr"/>
       <c r="F201" s="2" t="inlineStr"/>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges are present on the proposed development site</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
@@ -6882,11 +6942,19 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n"/>
-      <c r="B202" s="2" t="n"/>
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Trade effluent</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
+        </is>
+      </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Trees on adjacent land</t>
+          <t>Disposal required</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr"/>
@@ -6894,7 +6962,7 @@
       <c r="F202" s="2" t="inlineStr"/>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
+          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -6909,72 +6977,64 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="inlineStr">
-        <is>
-          <t>Vehicle parking</t>
-        </is>
-      </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
-        </is>
-      </c>
+      <c r="A203" s="2" t="n"/>
+      <c r="B203" s="2" t="n"/>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Parking spaces[]</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="inlineStr">
-        <is>
-          <t>Parking space type</t>
-        </is>
-      </c>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr"/>
       <c r="E203" s="2" t="inlineStr"/>
       <c r="F203" s="2" t="inlineStr"/>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>Type of parking space or vehicle type</t>
+          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n"/>
-      <c r="B204" s="2" t="n"/>
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Trees and hedges information</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+        </is>
+      </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Parking spaces[]</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="inlineStr">
-        <is>
-          <t>Vehicle type other</t>
-        </is>
-      </c>
+          <t>Trees on site</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr"/>
       <c r="E204" s="2" t="inlineStr"/>
       <c r="F204" s="2" t="inlineStr"/>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>Vehicle type when parking space type is 'other'</t>
+          <t>Whether trees or hedges are present on the proposed development site</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6983,24 +7043,20 @@
       <c r="B205" s="2" t="n"/>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>Parking spaces[]</t>
-        </is>
-      </c>
-      <c r="D205" s="2" t="inlineStr">
-        <is>
-          <t>Total existing</t>
-        </is>
-      </c>
+          <t>Trees on adjacent land</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr"/>
       <c r="E205" s="2" t="inlineStr"/>
       <c r="F205" s="2" t="inlineStr"/>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>Total number of existing parking spaces</t>
+          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr">
@@ -7010,8 +7066,16 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n"/>
-      <c r="B206" s="2" t="n"/>
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Vehicle parking</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
+        </is>
+      </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
           <t>Parking spaces[]</t>
@@ -7019,19 +7083,19 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Total proposed</t>
+          <t>Parking space type</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr"/>
       <c r="F206" s="2" t="inlineStr"/>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Total number of proposed parking spaces</t>
+          <t>Type of parking space or vehicle type</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I206" s="2" t="inlineStr">
@@ -7050,54 +7114,50 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Difference in spaces</t>
+          <t>Vehicle type other</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr"/>
       <c r="F207" s="2" t="inlineStr"/>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>Net change in parking spaces (proposed minus existing)</t>
+          <t>Vehicle type when parking space type is 'other'</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="inlineStr">
-        <is>
-          <t>Waste storage and collection</t>
-        </is>
-      </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
-        </is>
-      </c>
+      <c r="A208" s="2" t="n"/>
+      <c r="B208" s="2" t="n"/>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Needs waste storage area</t>
-        </is>
-      </c>
-      <c r="D208" s="2" t="inlineStr"/>
+          <t>Parking spaces[]</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>Total existing</t>
+        </is>
+      </c>
       <c r="E208" s="2" t="inlineStr"/>
       <c r="F208" s="2" t="inlineStr"/>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal require a waste storage area</t>
+          <t>Total number of existing parking spaces</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I208" s="2" t="inlineStr">
@@ -7111,25 +7171,29 @@
       <c r="B209" s="2" t="n"/>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Waste storage area details</t>
-        </is>
-      </c>
-      <c r="D209" s="2" t="inlineStr"/>
+          <t>Parking spaces[]</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>Total proposed</t>
+        </is>
+      </c>
       <c r="E209" s="2" t="inlineStr"/>
       <c r="F209" s="2" t="inlineStr"/>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>Details of the waste storage area including location, size, design and access arrangements</t>
+          <t>Total number of proposed parking spaces</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7138,20 +7202,24 @@
       <c r="B210" s="2" t="n"/>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Separate recycling arrangements</t>
-        </is>
-      </c>
-      <c r="D210" s="2" t="inlineStr"/>
+          <t>Parking spaces[]</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>Difference in spaces</t>
+        </is>
+      </c>
       <c r="E210" s="2" t="inlineStr"/>
       <c r="F210" s="2" t="inlineStr"/>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include separate recycling arrangements</t>
+          <t>Net change in parking spaces (proposed minus existing)</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr">
@@ -7161,11 +7229,19 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n"/>
-      <c r="B211" s="2" t="n"/>
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Waste storage and collection</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
+        </is>
+      </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>Separate recycling arrangements details</t>
+          <t>Needs waste storage area</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr"/>
@@ -7173,15 +7249,96 @@
       <c r="F211" s="2" t="inlineStr"/>
       <c r="G211" s="2" t="inlineStr">
         <is>
+          <t>Does the proposal require a waste storage area</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n"/>
+      <c r="B212" s="2" t="n"/>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>Waste storage area details</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr"/>
+      <c r="E212" s="2" t="inlineStr"/>
+      <c r="F212" s="2" t="inlineStr"/>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>Details of the waste storage area including location, size, design and access arrangements</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n"/>
+      <c r="B213" s="2" t="n"/>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>Separate recycling arrangements</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr"/>
+      <c r="E213" s="2" t="inlineStr"/>
+      <c r="F213" s="2" t="inlineStr"/>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>Does the proposal include separate recycling arrangements</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n"/>
+      <c r="B214" s="2" t="n"/>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>Separate recycling arrangements details</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr"/>
+      <c r="E214" s="2" t="inlineStr"/>
+      <c r="F214" s="2" t="inlineStr"/>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
           <t>Details of the recycling arrangements including types of materials, collection methods and storage facilities</t>
         </is>
       </c>
-      <c r="H211" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I211" s="2" t="inlineStr">
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
@@ -7189,68 +7346,68 @@
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="B65"/>
-    <mergeCell ref="A94:A97"/>
-    <mergeCell ref="B193:B198"/>
-    <mergeCell ref="B94:B97"/>
-    <mergeCell ref="B199:B200"/>
-    <mergeCell ref="B148:B158"/>
+    <mergeCell ref="B53:B66"/>
+    <mergeCell ref="B118:B129"/>
+    <mergeCell ref="B96:B99"/>
+    <mergeCell ref="B68:B70"/>
     <mergeCell ref="A2:A19"/>
-    <mergeCell ref="B72:B77"/>
-    <mergeCell ref="A203:A207"/>
-    <mergeCell ref="B208:B211"/>
-    <mergeCell ref="B182:B183"/>
-    <mergeCell ref="A208:A211"/>
-    <mergeCell ref="A30:A37"/>
-    <mergeCell ref="A128:A142"/>
-    <mergeCell ref="B98:B101"/>
-    <mergeCell ref="A88:A93"/>
-    <mergeCell ref="B143:B147"/>
-    <mergeCell ref="B51:B64"/>
-    <mergeCell ref="A184:A192"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="B66:B68"/>
-    <mergeCell ref="A143:A147"/>
-    <mergeCell ref="B166:B181"/>
-    <mergeCell ref="B42:B47"/>
-    <mergeCell ref="A159:A165"/>
-    <mergeCell ref="A193:A198"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A78:A87"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="B88:B93"/>
+    <mergeCell ref="A104:A110"/>
+    <mergeCell ref="B90:B95"/>
+    <mergeCell ref="B146:B150"/>
+    <mergeCell ref="A151:A161"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="A67"/>
+    <mergeCell ref="B162:B168"/>
+    <mergeCell ref="A53:A66"/>
+    <mergeCell ref="A206:A210"/>
+    <mergeCell ref="B151:B161"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="B187:B195"/>
+    <mergeCell ref="A196:A201"/>
+    <mergeCell ref="A130:A145"/>
+    <mergeCell ref="A204:A205"/>
+    <mergeCell ref="A90:A95"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A185:A186"/>
+    <mergeCell ref="B206:B210"/>
+    <mergeCell ref="A111:A117"/>
+    <mergeCell ref="B30:B38"/>
+    <mergeCell ref="A43:A49"/>
+    <mergeCell ref="A74:A79"/>
+    <mergeCell ref="B169:B184"/>
+    <mergeCell ref="B211:B214"/>
     <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A51:A64"/>
-    <mergeCell ref="B201:B202"/>
-    <mergeCell ref="A65"/>
-    <mergeCell ref="B109:B115"/>
-    <mergeCell ref="A69:A71"/>
-    <mergeCell ref="B203:B207"/>
-    <mergeCell ref="B128:B142"/>
-    <mergeCell ref="B159:B165"/>
-    <mergeCell ref="A199:A200"/>
-    <mergeCell ref="B116:B127"/>
-    <mergeCell ref="A166:A181"/>
-    <mergeCell ref="A66:A68"/>
-    <mergeCell ref="A42:A47"/>
-    <mergeCell ref="B78:B87"/>
-    <mergeCell ref="B184:B192"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A148:A158"/>
+    <mergeCell ref="B104:B110"/>
+    <mergeCell ref="A118:A129"/>
+    <mergeCell ref="A100:A103"/>
+    <mergeCell ref="B196:B201"/>
+    <mergeCell ref="A169:A184"/>
+    <mergeCell ref="B71:B73"/>
+    <mergeCell ref="A80:A89"/>
+    <mergeCell ref="B130:B145"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="B67"/>
+    <mergeCell ref="B204:B205"/>
+    <mergeCell ref="B185:B186"/>
+    <mergeCell ref="A30:A38"/>
+    <mergeCell ref="A202:A203"/>
+    <mergeCell ref="B43:B49"/>
+    <mergeCell ref="B74:B79"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="A211:A214"/>
+    <mergeCell ref="A96:A99"/>
     <mergeCell ref="B26:B29"/>
-    <mergeCell ref="B30:B37"/>
     <mergeCell ref="A20:A25"/>
-    <mergeCell ref="A201:A202"/>
     <mergeCell ref="B20:B25"/>
-    <mergeCell ref="A72:A77"/>
+    <mergeCell ref="A39:A42"/>
     <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B69:B71"/>
-    <mergeCell ref="B102:B108"/>
-    <mergeCell ref="A182:A183"/>
-    <mergeCell ref="A116:A127"/>
-    <mergeCell ref="A98:A101"/>
+    <mergeCell ref="B100:B103"/>
+    <mergeCell ref="B111:B117"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="A146:A150"/>
+    <mergeCell ref="A187:A195"/>
+    <mergeCell ref="B80:B89"/>
+    <mergeCell ref="A162:A168"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
